--- a/docs/live-data/futuristic-vessel-timeseries-template.xlsx
+++ b/docs/live-data/futuristic-vessel-timeseries-template.xlsx
@@ -9,8 +9,11 @@
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="TIMESERIES" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ONTOLOGY" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ONTOLOGY'!$A$1:$F$62</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -44,7 +47,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -64,6 +67,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -89,12 +97,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -103,6 +114,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -468,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -522,12 +534,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sample data: 30 min every 5 s under way; genset 1's cylinder 4 exhaust rises over 400 C for a quarter of an hour.</t>
+          <t>Names: a blue name in row 2 is a property the ontology has (the KG workbook's own name for it); an orange one is proposed, not in the ontology yet.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
+        <is>
+          <t>The ONTOLOGY sheet maps every column to its ontology property, or to the property proposed for it, with its unit and what the ontology has nearest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sample data: 30 min every 5 s under way; genset 1's cylinder 4 exhaust rises over 400 C for a quarter of an hour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Into the viewer: python scripts/convert-timeseries.py &lt;this.xlsx&gt; (see docs/live-data/futuristic-vessel-timeseries.md).</t>
         </is>
@@ -684,197 +710,197 @@
           <t>TIMESTAMP-UTC</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-LATITUDE-IN-DEG</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-LONGITUDE-IN-DEG</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-HEADING-IN-DEG</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-COURSE-OVER-GROUND-IN-DEG</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-SPEED-OVER-GROUND-IN-KN</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-SPEED-THROUGH-WATER-IN-KN</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-RATE-OF-TURN-IN-DEG_PER_MIN</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-DRAFT-FORE-IN-M</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-DRAFT-AFT-IN-M</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-ROLL-IN-DEG</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-PITCH-IN-DEG</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-HEAVE-IN-M</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-OPERATIONAL-MODE</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-AUTONOMY-LEVEL</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-DISTANCE-TO-GO-IN-NM</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="Q2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-TRUE-WIND-SPEED-IN-KN</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="R2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-TRUE-WIND-DIRECTION-IN-DEG</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="S2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-SIGNIFICANT-WAVE-HEIGHT-IN-M</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr">
+      <c r="T2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-CLOUD-COVER-PERCENTAGE</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr">
+      <c r="U2" s="5" t="inlineStr">
         <is>
           <t>FV-RR-1.TWINSHIP-PRECIPITATION-IN-MM_PER_HR</t>
         </is>
       </c>
       <c r="V2" s="4" t="inlineStr">
         <is>
-          <t>FV-GN-1.TWINSHIP-SHAFT-SPEED-IN-REV_PER_MIN</t>
-        </is>
-      </c>
-      <c r="W2" s="4" t="inlineStr">
+          <t>FV-GN-1.TWINSHIP-DIESEL-ENGINE-SPEED-IN-REV-PER-MIN</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
         <is>
           <t>FV-GN-1.TWINSHIP-GENERATOR-POWER-IN-KW</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="X2" s="5" t="inlineStr">
         <is>
           <t>FV-GN-1.TWINSHIP-LOAD-PERCENTAGE</t>
         </is>
       </c>
       <c r="Y2" s="4" t="inlineStr">
         <is>
-          <t>FV-GN-1.TWINSHIP-FUEL-CONSUMPTION-RATE-IN-KG_PER_HR</t>
+          <t>FV-GN-1.TWINSHIP-FUEL-CONSUMPTION-RATE-IN-MT_PER_HR</t>
         </is>
       </c>
       <c r="Z2" s="4" t="inlineStr">
         <is>
-          <t>FV-GN-1.TWINSHIP-TOTAL-FUEL-CONSUMPTION-IN-MT</t>
+          <t>FV-GN-1.TWINSHIP-FUEL-CONSUMPTION-TOTAL-IN-MT</t>
         </is>
       </c>
       <c r="AA2" s="4" t="inlineStr">
         <is>
-          <t>FV-GN-1.TWINSHIP-COOLING-WATER-TEMPERATURE-IN-°C</t>
-        </is>
-      </c>
-      <c r="AB2" s="4" t="inlineStr">
+          <t>FV-GN-1.TWINSHIP-ME-COOLING-WATER-TEMPERATURE-IN-°C</t>
+        </is>
+      </c>
+      <c r="AB2" s="5" t="inlineStr">
         <is>
           <t>FV-GN-1.TWINSHIP-EXHAUST-GAS-TEMPERATURE-MAX-IN-°C</t>
         </is>
       </c>
-      <c r="AC2" s="4" t="inlineStr">
+      <c r="AC2" s="5" t="inlineStr">
         <is>
           <t>FV-GN-1.TWINSHIP-EXHAUST-GAS-TEMPERATURE-MAX-CYLINDER</t>
         </is>
       </c>
       <c r="AD2" s="4" t="inlineStr">
         <is>
-          <t>FV-GN-2.TWINSHIP-SHAFT-SPEED-IN-REV_PER_MIN</t>
-        </is>
-      </c>
-      <c r="AE2" s="4" t="inlineStr">
+          <t>FV-GN-2.TWINSHIP-DIESEL-ENGINE-SPEED-IN-REV-PER-MIN</t>
+        </is>
+      </c>
+      <c r="AE2" s="5" t="inlineStr">
         <is>
           <t>FV-GN-2.TWINSHIP-GENERATOR-POWER-IN-KW</t>
         </is>
       </c>
-      <c r="AF2" s="4" t="inlineStr">
+      <c r="AF2" s="5" t="inlineStr">
         <is>
           <t>FV-GN-2.TWINSHIP-LOAD-PERCENTAGE</t>
         </is>
       </c>
       <c r="AG2" s="4" t="inlineStr">
         <is>
-          <t>FV-GN-2.TWINSHIP-FUEL-CONSUMPTION-RATE-IN-KG_PER_HR</t>
+          <t>FV-GN-2.TWINSHIP-FUEL-CONSUMPTION-RATE-IN-MT_PER_HR</t>
         </is>
       </c>
       <c r="AH2" s="4" t="inlineStr">
         <is>
-          <t>FV-GN-2.TWINSHIP-TOTAL-FUEL-CONSUMPTION-IN-MT</t>
+          <t>FV-GN-2.TWINSHIP-FUEL-CONSUMPTION-TOTAL-IN-MT</t>
         </is>
       </c>
       <c r="AI2" s="4" t="inlineStr">
         <is>
-          <t>FV-GN-2.TWINSHIP-COOLING-WATER-TEMPERATURE-IN-°C</t>
-        </is>
-      </c>
-      <c r="AJ2" s="4" t="inlineStr">
+          <t>FV-GN-2.TWINSHIP-ME-COOLING-WATER-TEMPERATURE-IN-°C</t>
+        </is>
+      </c>
+      <c r="AJ2" s="5" t="inlineStr">
         <is>
           <t>FV-GN-2.TWINSHIP-EXHAUST-GAS-TEMPERATURE-MAX-IN-°C</t>
         </is>
       </c>
-      <c r="AK2" s="4" t="inlineStr">
+      <c r="AK2" s="5" t="inlineStr">
         <is>
           <t>FV-GN-2.TWINSHIP-EXHAUST-GAS-TEMPERATURE-MAX-CYLINDER</t>
         </is>
       </c>
-      <c r="AL2" s="4" t="inlineStr">
+      <c r="AL2" s="5" t="inlineStr">
         <is>
           <t>FV-ESS-1.TWINSHIP-ESS-STATE-OF-CHARGE-PERCENTAGE</t>
         </is>
       </c>
-      <c r="AM2" s="4" t="inlineStr">
+      <c r="AM2" s="5" t="inlineStr">
         <is>
           <t>FV-ESS-1.TWINSHIP-ESS-POWER-IN-KW</t>
         </is>
       </c>
-      <c r="AN2" s="4" t="inlineStr">
+      <c r="AN2" s="5" t="inlineStr">
         <is>
           <t>FV-EMSH-1.TWINSHIP-EMSH-POWER-IN-KW</t>
         </is>
@@ -886,10 +912,10 @@
       </c>
       <c r="AP2" s="4" t="inlineStr">
         <is>
-          <t>FV-EMSH-1.TWINSHIP-EMSH-TORQUE-kNm</t>
-        </is>
-      </c>
-      <c r="AQ2" s="4" t="inlineStr">
+          <t>FV-EMSH-1.TWINSHIP-EMSH-TORQUE-kN</t>
+        </is>
+      </c>
+      <c r="AQ2" s="5" t="inlineStr">
         <is>
           <t>FV-EMSH-2.TWINSHIP-EMSH-POWER-IN-KW</t>
         </is>
@@ -901,10 +927,10 @@
       </c>
       <c r="AS2" s="4" t="inlineStr">
         <is>
-          <t>FV-EMSH-2.TWINSHIP-EMSH-TORQUE-kNm</t>
-        </is>
-      </c>
-      <c r="AT2" s="4" t="inlineStr">
+          <t>FV-EMSH-2.TWINSHIP-EMSH-TORQUE-kN</t>
+        </is>
+      </c>
+      <c r="AT2" s="5" t="inlineStr">
         <is>
           <t>FV-CPP-1.TWINSHIP-CPP-PITCH-PERCENTAGE</t>
         </is>
@@ -914,7 +940,7 @@
           <t>FV-CPP-1.TWINSHIP-RUDDER-ANGLE-DEGREE</t>
         </is>
       </c>
-      <c r="AV2" s="4" t="inlineStr">
+      <c r="AV2" s="5" t="inlineStr">
         <is>
           <t>FV-CPP-2.TWINSHIP-CPP-PITCH-PERCENTAGE</t>
         </is>
@@ -934,12 +960,12 @@
           <t>FV-WASP-1.TWINSHIP-WASP-POWER-REDUCTION-EFFICIENCY-PERCENTAGE</t>
         </is>
       </c>
-      <c r="AZ2" s="4" t="inlineStr">
+      <c r="AZ2" s="5" t="inlineStr">
         <is>
           <t>FV-WASP-1.TWINSHIP-WASP-THRUST-IN-kN</t>
         </is>
       </c>
-      <c r="BA2" s="4" t="inlineStr">
+      <c r="BA2" s="5" t="inlineStr">
         <is>
           <t>FV-WASP-1.TWINSHIP-WASP-FAN-SPEED-IN-REV_PER_MIN</t>
         </is>
@@ -954,559 +980,559 @@
           <t>FV-WASP-2.TWINSHIP-WASP-POWER-REDUCTION-EFFICIENCY-PERCENTAGE</t>
         </is>
       </c>
-      <c r="BD2" s="4" t="inlineStr">
+      <c r="BD2" s="5" t="inlineStr">
         <is>
           <t>FV-WASP-2.TWINSHIP-WASP-THRUST-IN-kN</t>
         </is>
       </c>
-      <c r="BE2" s="4" t="inlineStr">
+      <c r="BE2" s="5" t="inlineStr">
         <is>
           <t>FV-WASP-2.TWINSHIP-WASP-FAN-SPEED-IN-REV_PER_MIN</t>
         </is>
       </c>
-      <c r="BF2" s="4" t="inlineStr">
+      <c r="BF2" s="5" t="inlineStr">
         <is>
           <t>SG-01.TWINSHIP-BENDING-STRESS-PERCENTAGE-OF-ALLOWABLE</t>
         </is>
       </c>
-      <c r="BG2" s="4" t="inlineStr">
+      <c r="BG2" s="5" t="inlineStr">
         <is>
           <t>SG-02.TWINSHIP-BENDING-STRESS-PERCENTAGE-OF-ALLOWABLE</t>
         </is>
       </c>
-      <c r="BH2" s="4" t="inlineStr">
+      <c r="BH2" s="5" t="inlineStr">
         <is>
           <t>SG-03.TWINSHIP-BENDING-STRESS-PERCENTAGE-OF-ALLOWABLE</t>
         </is>
       </c>
-      <c r="BI2" s="4" t="inlineStr">
+      <c r="BI2" s="5" t="inlineStr">
         <is>
           <t>SG-04.TWINSHIP-BENDING-STRESS-PERCENTAGE-OF-ALLOWABLE</t>
         </is>
       </c>
-      <c r="BJ2" s="4" t="inlineStr">
+      <c r="BJ2" s="5" t="inlineStr">
         <is>
           <t>SG-05.TWINSHIP-BENDING-STRESS-PERCENTAGE-OF-ALLOWABLE</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>DATETIME (ISO 8601, UTC)</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>ENUM (SAILING | MANOEUVRING | IN-PORT)</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>ENUM (L0 … L4)</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="S3" s="5" t="inlineStr">
+      <c r="S3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr">
+      <c r="T3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="U3" s="5" t="inlineStr">
+      <c r="U3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="V3" s="5" t="inlineStr">
+      <c r="V3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="W3" s="5" t="inlineStr">
+      <c r="W3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="X3" s="5" t="inlineStr">
+      <c r="X3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="Y3" s="5" t="inlineStr">
+      <c r="Y3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="Z3" s="5" t="inlineStr">
+      <c r="Z3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AA3" s="5" t="inlineStr">
+      <c r="AA3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AB3" s="5" t="inlineStr">
+      <c r="AB3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AC3" s="5" t="inlineStr">
+      <c r="AC3" s="6" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="AD3" s="5" t="inlineStr">
+      <c r="AD3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AE3" s="5" t="inlineStr">
+      <c r="AE3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AF3" s="5" t="inlineStr">
+      <c r="AF3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AG3" s="5" t="inlineStr">
+      <c r="AG3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AH3" s="5" t="inlineStr">
+      <c r="AH3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AI3" s="5" t="inlineStr">
+      <c r="AI3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AJ3" s="5" t="inlineStr">
+      <c r="AJ3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AK3" s="5" t="inlineStr">
+      <c r="AK3" s="6" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="AL3" s="5" t="inlineStr">
+      <c r="AL3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AM3" s="5" t="inlineStr">
+      <c r="AM3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AN3" s="5" t="inlineStr">
+      <c r="AN3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AO3" s="5" t="inlineStr">
+      <c r="AO3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AP3" s="5" t="inlineStr">
+      <c r="AP3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AQ3" s="5" t="inlineStr">
+      <c r="AQ3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AR3" s="5" t="inlineStr">
+      <c r="AR3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AS3" s="5" t="inlineStr">
+      <c r="AS3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AT3" s="5" t="inlineStr">
+      <c r="AT3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AU3" s="5" t="inlineStr">
+      <c r="AU3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AV3" s="5" t="inlineStr">
+      <c r="AV3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AW3" s="5" t="inlineStr">
+      <c r="AW3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AX3" s="5" t="inlineStr">
+      <c r="AX3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AY3" s="5" t="inlineStr">
+      <c r="AY3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="AZ3" s="5" t="inlineStr">
+      <c r="AZ3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="BA3" s="5" t="inlineStr">
+      <c r="BA3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="BB3" s="5" t="inlineStr">
+      <c r="BB3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="BC3" s="5" t="inlineStr">
+      <c r="BC3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="BD3" s="5" t="inlineStr">
+      <c r="BD3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="BE3" s="5" t="inlineStr">
+      <c r="BE3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="BF3" s="5" t="inlineStr">
+      <c r="BF3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="BG3" s="5" t="inlineStr">
+      <c r="BG3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="BH3" s="5" t="inlineStr">
+      <c r="BH3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="BI3" s="5" t="inlineStr">
+      <c r="BI3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
-      <c r="BJ3" s="5" t="inlineStr">
+      <c r="BJ3" s="6" t="inlineStr">
         <is>
           <t>DOUBLE</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>WARNING AT</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="n">
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
+      <c r="K4" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="L4" s="6" t="n"/>
-      <c r="M4" s="6" t="n"/>
-      <c r="N4" s="6" t="n"/>
-      <c r="O4" s="6" t="n"/>
-      <c r="P4" s="6" t="n"/>
-      <c r="Q4" s="6" t="n">
+      <c r="L4" s="7" t="n"/>
+      <c r="M4" s="7" t="n"/>
+      <c r="N4" s="7" t="n"/>
+      <c r="O4" s="7" t="n"/>
+      <c r="P4" s="7" t="n"/>
+      <c r="Q4" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="R4" s="6" t="n"/>
-      <c r="S4" s="6" t="n">
+      <c r="R4" s="7" t="n"/>
+      <c r="S4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="T4" s="6" t="n"/>
-      <c r="U4" s="6" t="n"/>
-      <c r="V4" s="6" t="n"/>
-      <c r="W4" s="6" t="n"/>
-      <c r="X4" s="6" t="n">
+      <c r="T4" s="7" t="n"/>
+      <c r="U4" s="7" t="n"/>
+      <c r="V4" s="7" t="n"/>
+      <c r="W4" s="7" t="n"/>
+      <c r="X4" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="Y4" s="6" t="n"/>
-      <c r="Z4" s="6" t="n"/>
-      <c r="AA4" s="6" t="n">
+      <c r="Y4" s="7" t="n"/>
+      <c r="Z4" s="7" t="n"/>
+      <c r="AA4" s="7" t="n">
         <v>88</v>
       </c>
-      <c r="AB4" s="6" t="n">
+      <c r="AB4" s="7" t="n">
         <v>400</v>
       </c>
-      <c r="AC4" s="6" t="n"/>
-      <c r="AD4" s="6" t="n"/>
-      <c r="AE4" s="6" t="n"/>
-      <c r="AF4" s="6" t="n">
+      <c r="AC4" s="7" t="n"/>
+      <c r="AD4" s="7" t="n"/>
+      <c r="AE4" s="7" t="n"/>
+      <c r="AF4" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="AG4" s="6" t="n"/>
-      <c r="AH4" s="6" t="n"/>
-      <c r="AI4" s="6" t="n">
+      <c r="AG4" s="7" t="n"/>
+      <c r="AH4" s="7" t="n"/>
+      <c r="AI4" s="7" t="n">
         <v>88</v>
       </c>
-      <c r="AJ4" s="6" t="n">
+      <c r="AJ4" s="7" t="n">
         <v>400</v>
       </c>
-      <c r="AK4" s="6" t="n"/>
-      <c r="AL4" s="6" t="inlineStr">
+      <c r="AK4" s="7" t="n"/>
+      <c r="AL4" s="7" t="inlineStr">
         <is>
           <t>&lt;25</t>
         </is>
       </c>
-      <c r="AM4" s="6" t="n"/>
-      <c r="AN4" s="6" t="n"/>
-      <c r="AO4" s="6" t="n">
+      <c r="AM4" s="7" t="n"/>
+      <c r="AN4" s="7" t="n"/>
+      <c r="AO4" s="7" t="n">
         <v>155</v>
       </c>
-      <c r="AP4" s="6" t="n"/>
-      <c r="AQ4" s="6" t="n"/>
-      <c r="AR4" s="6" t="n">
+      <c r="AP4" s="7" t="n"/>
+      <c r="AQ4" s="7" t="n"/>
+      <c r="AR4" s="7" t="n">
         <v>155</v>
       </c>
-      <c r="AS4" s="6" t="n"/>
-      <c r="AT4" s="6" t="n"/>
-      <c r="AU4" s="6" t="n"/>
-      <c r="AV4" s="6" t="n"/>
-      <c r="AW4" s="6" t="n"/>
-      <c r="AX4" s="6" t="n"/>
-      <c r="AY4" s="6" t="n"/>
-      <c r="AZ4" s="6" t="n"/>
-      <c r="BA4" s="6" t="n"/>
-      <c r="BB4" s="6" t="n"/>
-      <c r="BC4" s="6" t="n"/>
-      <c r="BD4" s="6" t="n"/>
-      <c r="BE4" s="6" t="n"/>
-      <c r="BF4" s="6" t="n">
+      <c r="AS4" s="7" t="n"/>
+      <c r="AT4" s="7" t="n"/>
+      <c r="AU4" s="7" t="n"/>
+      <c r="AV4" s="7" t="n"/>
+      <c r="AW4" s="7" t="n"/>
+      <c r="AX4" s="7" t="n"/>
+      <c r="AY4" s="7" t="n"/>
+      <c r="AZ4" s="7" t="n"/>
+      <c r="BA4" s="7" t="n"/>
+      <c r="BB4" s="7" t="n"/>
+      <c r="BC4" s="7" t="n"/>
+      <c r="BD4" s="7" t="n"/>
+      <c r="BE4" s="7" t="n"/>
+      <c r="BF4" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="BG4" s="6" t="n">
+      <c r="BG4" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="BH4" s="6" t="n">
+      <c r="BH4" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="BI4" s="6" t="n">
+      <c r="BI4" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="BJ4" s="6" t="n">
+      <c r="BJ4" s="7" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>ALARM AT</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n">
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="L5" s="6" t="n"/>
-      <c r="M5" s="6" t="n"/>
-      <c r="N5" s="6" t="n"/>
-      <c r="O5" s="6" t="n"/>
-      <c r="P5" s="6" t="n"/>
-      <c r="Q5" s="6" t="n">
+      <c r="L5" s="7" t="n"/>
+      <c r="M5" s="7" t="n"/>
+      <c r="N5" s="7" t="n"/>
+      <c r="O5" s="7" t="n"/>
+      <c r="P5" s="7" t="n"/>
+      <c r="Q5" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="R5" s="6" t="n"/>
-      <c r="S5" s="6" t="n">
+      <c r="R5" s="7" t="n"/>
+      <c r="S5" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="T5" s="6" t="n"/>
-      <c r="U5" s="6" t="n"/>
-      <c r="V5" s="6" t="n"/>
-      <c r="W5" s="6" t="n"/>
-      <c r="X5" s="6" t="n">
+      <c r="T5" s="7" t="n"/>
+      <c r="U5" s="7" t="n"/>
+      <c r="V5" s="7" t="n"/>
+      <c r="W5" s="7" t="n"/>
+      <c r="X5" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="Y5" s="6" t="n"/>
-      <c r="Z5" s="6" t="n"/>
-      <c r="AA5" s="6" t="n">
+      <c r="Y5" s="7" t="n"/>
+      <c r="Z5" s="7" t="n"/>
+      <c r="AA5" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="AB5" s="6" t="n">
+      <c r="AB5" s="7" t="n">
         <v>420</v>
       </c>
-      <c r="AC5" s="6" t="n"/>
-      <c r="AD5" s="6" t="n"/>
-      <c r="AE5" s="6" t="n"/>
-      <c r="AF5" s="6" t="n">
+      <c r="AC5" s="7" t="n"/>
+      <c r="AD5" s="7" t="n"/>
+      <c r="AE5" s="7" t="n"/>
+      <c r="AF5" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="AG5" s="6" t="n"/>
-      <c r="AH5" s="6" t="n"/>
-      <c r="AI5" s="6" t="n">
+      <c r="AG5" s="7" t="n"/>
+      <c r="AH5" s="7" t="n"/>
+      <c r="AI5" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="AJ5" s="6" t="n">
+      <c r="AJ5" s="7" t="n">
         <v>420</v>
       </c>
-      <c r="AK5" s="6" t="n"/>
-      <c r="AL5" s="6" t="inlineStr">
+      <c r="AK5" s="7" t="n"/>
+      <c r="AL5" s="7" t="inlineStr">
         <is>
           <t>&lt;15</t>
         </is>
       </c>
-      <c r="AM5" s="6" t="n"/>
-      <c r="AN5" s="6" t="n"/>
-      <c r="AO5" s="6" t="n">
+      <c r="AM5" s="7" t="n"/>
+      <c r="AN5" s="7" t="n"/>
+      <c r="AO5" s="7" t="n">
         <v>165</v>
       </c>
-      <c r="AP5" s="6" t="n"/>
-      <c r="AQ5" s="6" t="n"/>
-      <c r="AR5" s="6" t="n">
+      <c r="AP5" s="7" t="n"/>
+      <c r="AQ5" s="7" t="n"/>
+      <c r="AR5" s="7" t="n">
         <v>165</v>
       </c>
-      <c r="AS5" s="6" t="n"/>
-      <c r="AT5" s="6" t="n"/>
-      <c r="AU5" s="6" t="n"/>
-      <c r="AV5" s="6" t="n"/>
-      <c r="AW5" s="6" t="n"/>
-      <c r="AX5" s="6" t="n"/>
-      <c r="AY5" s="6" t="n"/>
-      <c r="AZ5" s="6" t="n"/>
-      <c r="BA5" s="6" t="n"/>
-      <c r="BB5" s="6" t="n"/>
-      <c r="BC5" s="6" t="n"/>
-      <c r="BD5" s="6" t="n"/>
-      <c r="BE5" s="6" t="n"/>
-      <c r="BF5" s="6" t="n">
+      <c r="AS5" s="7" t="n"/>
+      <c r="AT5" s="7" t="n"/>
+      <c r="AU5" s="7" t="n"/>
+      <c r="AV5" s="7" t="n"/>
+      <c r="AW5" s="7" t="n"/>
+      <c r="AX5" s="7" t="n"/>
+      <c r="AY5" s="7" t="n"/>
+      <c r="AZ5" s="7" t="n"/>
+      <c r="BA5" s="7" t="n"/>
+      <c r="BB5" s="7" t="n"/>
+      <c r="BC5" s="7" t="n"/>
+      <c r="BD5" s="7" t="n"/>
+      <c r="BE5" s="7" t="n"/>
+      <c r="BF5" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="BG5" s="6" t="n">
+      <c r="BG5" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="BH5" s="6" t="n">
+      <c r="BH5" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="BI5" s="6" t="n">
+      <c r="BI5" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="BJ5" s="6" t="n">
+      <c r="BJ5" s="7" t="n">
         <v>90</v>
       </c>
     </row>
@@ -1590,7 +1616,7 @@
         <v>82.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>973.1</v>
+        <v>0.9731</v>
       </c>
       <c r="Z6" t="n">
         <v>812.401</v>
@@ -1614,7 +1640,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>969.5</v>
+        <v>0.9695</v>
       </c>
       <c r="AH6" t="n">
         <v>798.101</v>
@@ -1784,7 +1810,7 @@
         <v>82.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>975.3</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="Z7" t="n">
         <v>812.403</v>
@@ -1808,7 +1834,7 @@
         <v>81.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>969.3</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="AH7" t="n">
         <v>798.103</v>
@@ -1978,7 +2004,7 @@
         <v>82</v>
       </c>
       <c r="Y8" t="n">
-        <v>970.7</v>
+        <v>0.9707</v>
       </c>
       <c r="Z8" t="n">
         <v>812.404</v>
@@ -2002,7 +2028,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG8" t="n">
-        <v>969.8</v>
+        <v>0.9698</v>
       </c>
       <c r="AH8" t="n">
         <v>798.104</v>
@@ -2172,7 +2198,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>964.3</v>
+        <v>0.9643</v>
       </c>
       <c r="Z9" t="n">
         <v>812.405</v>
@@ -2196,7 +2222,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG9" t="n">
-        <v>969.9</v>
+        <v>0.9699</v>
       </c>
       <c r="AH9" t="n">
         <v>798.105</v>
@@ -2366,7 +2392,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>960.4</v>
+        <v>0.9604</v>
       </c>
       <c r="Z10" t="n">
         <v>812.407</v>
@@ -2390,7 +2416,7 @@
         <v>82</v>
       </c>
       <c r="AG10" t="n">
-        <v>971.4</v>
+        <v>0.9714</v>
       </c>
       <c r="AH10" t="n">
         <v>798.107</v>
@@ -2560,7 +2586,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="Y11" t="n">
-        <v>965.9</v>
+        <v>0.9659</v>
       </c>
       <c r="Z11" t="n">
         <v>812.408</v>
@@ -2584,7 +2610,7 @@
         <v>81.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>968.5</v>
+        <v>0.9685</v>
       </c>
       <c r="AH11" t="n">
         <v>798.1079999999999</v>
@@ -2754,7 +2780,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>966.3</v>
+        <v>0.9663</v>
       </c>
       <c r="Z12" t="n">
         <v>812.409</v>
@@ -2778,7 +2804,7 @@
         <v>81.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>964.7</v>
+        <v>0.9647</v>
       </c>
       <c r="AH12" t="n">
         <v>798.109</v>
@@ -2948,7 +2974,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="Y13" t="n">
-        <v>964.7</v>
+        <v>0.9647</v>
       </c>
       <c r="Z13" t="n">
         <v>812.4109999999999</v>
@@ -2972,7 +2998,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="AG13" t="n">
-        <v>960.9</v>
+        <v>0.9609</v>
       </c>
       <c r="AH13" t="n">
         <v>798.111</v>
@@ -3142,7 +3168,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="Y14" t="n">
-        <v>960.5</v>
+        <v>0.9605</v>
       </c>
       <c r="Z14" t="n">
         <v>812.412</v>
@@ -3166,7 +3192,7 @@
         <v>80.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>956.6</v>
+        <v>0.9566</v>
       </c>
       <c r="AH14" t="n">
         <v>798.112</v>
@@ -3336,7 +3362,7 @@
         <v>80.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>956.4</v>
+        <v>0.9564</v>
       </c>
       <c r="Z15" t="n">
         <v>812.413</v>
@@ -3360,7 +3386,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="AG15" t="n">
-        <v>958.3</v>
+        <v>0.9583</v>
       </c>
       <c r="AH15" t="n">
         <v>798.1130000000001</v>
@@ -3530,7 +3556,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="Y16" t="n">
-        <v>961.1</v>
+        <v>0.9611</v>
       </c>
       <c r="Z16" t="n">
         <v>812.415</v>
@@ -3554,7 +3580,7 @@
         <v>81.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>965</v>
+        <v>0.965</v>
       </c>
       <c r="AH16" t="n">
         <v>798.115</v>
@@ -3724,7 +3750,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="Y17" t="n">
-        <v>964</v>
+        <v>0.964</v>
       </c>
       <c r="Z17" t="n">
         <v>812.4160000000001</v>
@@ -3748,7 +3774,7 @@
         <v>81.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>961.8</v>
+        <v>0.9618</v>
       </c>
       <c r="AH17" t="n">
         <v>798.116</v>
@@ -3918,7 +3944,7 @@
         <v>81.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>967.7</v>
+        <v>0.9677</v>
       </c>
       <c r="Z18" t="n">
         <v>812.417</v>
@@ -3942,7 +3968,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG18" t="n">
-        <v>966</v>
+        <v>0.966</v>
       </c>
       <c r="AH18" t="n">
         <v>798.117</v>
@@ -4112,7 +4138,7 @@
         <v>82.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>974.2</v>
+        <v>0.9742</v>
       </c>
       <c r="Z19" t="n">
         <v>812.419</v>
@@ -4136,7 +4162,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG19" t="n">
-        <v>969.8</v>
+        <v>0.9698</v>
       </c>
       <c r="AH19" t="n">
         <v>798.119</v>
@@ -4306,7 +4332,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="Y20" t="n">
-        <v>970.2</v>
+        <v>0.9702</v>
       </c>
       <c r="Z20" t="n">
         <v>812.42</v>
@@ -4330,7 +4356,7 @@
         <v>82.3</v>
       </c>
       <c r="AG20" t="n">
-        <v>974.4</v>
+        <v>0.9744</v>
       </c>
       <c r="AH20" t="n">
         <v>798.12</v>
@@ -4500,7 +4526,7 @@
         <v>81.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>968.4</v>
+        <v>0.9684</v>
       </c>
       <c r="Z21" t="n">
         <v>812.421</v>
@@ -4524,7 +4550,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG21" t="n">
-        <v>970.6</v>
+        <v>0.9706</v>
       </c>
       <c r="AH21" t="n">
         <v>798.121</v>
@@ -4694,7 +4720,7 @@
         <v>82</v>
       </c>
       <c r="Y22" t="n">
-        <v>970.9</v>
+        <v>0.9709</v>
       </c>
       <c r="Z22" t="n">
         <v>812.423</v>
@@ -4718,7 +4744,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="AG22" t="n">
-        <v>971.8</v>
+        <v>0.9718</v>
       </c>
       <c r="AH22" t="n">
         <v>798.123</v>
@@ -4888,7 +4914,7 @@
         <v>81.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>969.3</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="Z23" t="n">
         <v>812.424</v>
@@ -4912,7 +4938,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="AG23" t="n">
-        <v>976.1</v>
+        <v>0.9761</v>
       </c>
       <c r="AH23" t="n">
         <v>798.124</v>
@@ -5082,7 +5108,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="Y24" t="n">
-        <v>964.7</v>
+        <v>0.9647</v>
       </c>
       <c r="Z24" t="n">
         <v>812.426</v>
@@ -5106,7 +5132,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="AG24" t="n">
-        <v>976.1</v>
+        <v>0.9761</v>
       </c>
       <c r="AH24" t="n">
         <v>798.126</v>
@@ -5276,7 +5302,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="Y25" t="n">
-        <v>964.6</v>
+        <v>0.9646</v>
       </c>
       <c r="Z25" t="n">
         <v>812.427</v>
@@ -5300,7 +5326,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG25" t="n">
-        <v>969.8</v>
+        <v>0.9698</v>
       </c>
       <c r="AH25" t="n">
         <v>798.127</v>
@@ -5470,7 +5496,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="Y26" t="n">
-        <v>972.2</v>
+        <v>0.9722</v>
       </c>
       <c r="Z26" t="n">
         <v>812.428</v>
@@ -5494,7 +5520,7 @@
         <v>81.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>967.5</v>
+        <v>0.9675</v>
       </c>
       <c r="AH26" t="n">
         <v>798.128</v>
@@ -5664,7 +5690,7 @@
         <v>81.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>965.7</v>
+        <v>0.9657</v>
       </c>
       <c r="Z27" t="n">
         <v>812.4299999999999</v>
@@ -5688,7 +5714,7 @@
         <v>81.8</v>
       </c>
       <c r="AG27" t="n">
-        <v>969.4</v>
+        <v>0.9694</v>
       </c>
       <c r="AH27" t="n">
         <v>798.13</v>
@@ -5858,7 +5884,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="Y28" t="n">
-        <v>960.3</v>
+        <v>0.9603</v>
       </c>
       <c r="Z28" t="n">
         <v>812.431</v>
@@ -5882,7 +5908,7 @@
         <v>81.3</v>
       </c>
       <c r="AG28" t="n">
-        <v>962.4</v>
+        <v>0.9624</v>
       </c>
       <c r="AH28" t="n">
         <v>798.131</v>
@@ -6052,7 +6078,7 @@
         <v>80.7</v>
       </c>
       <c r="Y29" t="n">
-        <v>955.8</v>
+        <v>0.9558</v>
       </c>
       <c r="Z29" t="n">
         <v>812.432</v>
@@ -6076,7 +6102,7 @@
         <v>80.8</v>
       </c>
       <c r="AG29" t="n">
-        <v>957.1</v>
+        <v>0.9571</v>
       </c>
       <c r="AH29" t="n">
         <v>798.1319999999999</v>
@@ -6246,7 +6272,7 @@
         <v>80.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>950</v>
+        <v>0.95</v>
       </c>
       <c r="Z30" t="n">
         <v>812.434</v>
@@ -6270,7 +6296,7 @@
         <v>80.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>953.8</v>
+        <v>0.9538</v>
       </c>
       <c r="AH30" t="n">
         <v>798.134</v>
@@ -6440,7 +6466,7 @@
         <v>80.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>953.7</v>
+        <v>0.9537</v>
       </c>
       <c r="Z31" t="n">
         <v>812.4349999999999</v>
@@ -6464,7 +6490,7 @@
         <v>80.09999999999999</v>
       </c>
       <c r="AG31" t="n">
-        <v>948.2</v>
+        <v>0.9482</v>
       </c>
       <c r="AH31" t="n">
         <v>798.135</v>
@@ -6634,7 +6660,7 @@
         <v>80.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>953</v>
+        <v>0.953</v>
       </c>
       <c r="Z32" t="n">
         <v>812.436</v>
@@ -6658,7 +6684,7 @@
         <v>80.2</v>
       </c>
       <c r="AG32" t="n">
-        <v>949.3</v>
+        <v>0.9493</v>
       </c>
       <c r="AH32" t="n">
         <v>798.136</v>
@@ -6828,7 +6854,7 @@
         <v>81</v>
       </c>
       <c r="Y33" t="n">
-        <v>958.9</v>
+        <v>0.9589</v>
       </c>
       <c r="Z33" t="n">
         <v>812.438</v>
@@ -6852,7 +6878,7 @@
         <v>79.8</v>
       </c>
       <c r="AG33" t="n">
-        <v>945.3</v>
+        <v>0.9453</v>
       </c>
       <c r="AH33" t="n">
         <v>798.138</v>
@@ -7022,7 +7048,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="Y34" t="n">
-        <v>964.6</v>
+        <v>0.9646</v>
       </c>
       <c r="Z34" t="n">
         <v>812.439</v>
@@ -7046,7 +7072,7 @@
         <v>79.59999999999999</v>
       </c>
       <c r="AG34" t="n">
-        <v>943.1</v>
+        <v>0.9431</v>
       </c>
       <c r="AH34" t="n">
         <v>798.139</v>
@@ -7216,7 +7242,7 @@
         <v>81.7</v>
       </c>
       <c r="Y35" t="n">
-        <v>967.1</v>
+        <v>0.9671</v>
       </c>
       <c r="Z35" t="n">
         <v>812.4400000000001</v>
@@ -7240,7 +7266,7 @@
         <v>80.2</v>
       </c>
       <c r="AG35" t="n">
-        <v>950.3</v>
+        <v>0.9503</v>
       </c>
       <c r="AH35" t="n">
         <v>798.14</v>
@@ -7410,7 +7436,7 @@
         <v>81.8</v>
       </c>
       <c r="Y36" t="n">
-        <v>969.4</v>
+        <v>0.9694</v>
       </c>
       <c r="Z36" t="n">
         <v>812.442</v>
@@ -7434,7 +7460,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="AG36" t="n">
-        <v>954.7</v>
+        <v>0.9547</v>
       </c>
       <c r="AH36" t="n">
         <v>798.141</v>
@@ -7604,7 +7630,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="Y37" t="n">
-        <v>966.9</v>
+        <v>0.9669</v>
       </c>
       <c r="Z37" t="n">
         <v>812.443</v>
@@ -7628,7 +7654,7 @@
         <v>81.2</v>
       </c>
       <c r="AG37" t="n">
-        <v>962.3</v>
+        <v>0.9623</v>
       </c>
       <c r="AH37" t="n">
         <v>798.143</v>
@@ -7798,7 +7824,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="Y38" t="n">
-        <v>972.3</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="Z38" t="n">
         <v>812.444</v>
@@ -7822,7 +7848,7 @@
         <v>81.3</v>
       </c>
       <c r="AG38" t="n">
-        <v>962.5</v>
+        <v>0.9625</v>
       </c>
       <c r="AH38" t="n">
         <v>798.144</v>
@@ -7992,7 +8018,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="Y39" t="n">
-        <v>976.3</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="Z39" t="n">
         <v>812.446</v>
@@ -8016,7 +8042,7 @@
         <v>81.7</v>
       </c>
       <c r="AG39" t="n">
-        <v>968.1</v>
+        <v>0.9681</v>
       </c>
       <c r="AH39" t="n">
         <v>798.145</v>
@@ -8186,7 +8212,7 @@
         <v>82.2</v>
       </c>
       <c r="Y40" t="n">
-        <v>973.2</v>
+        <v>0.9732</v>
       </c>
       <c r="Z40" t="n">
         <v>812.447</v>
@@ -8210,7 +8236,7 @@
         <v>82.3</v>
       </c>
       <c r="AG40" t="n">
-        <v>974.3</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="AH40" t="n">
         <v>798.147</v>
@@ -8380,7 +8406,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="Y41" t="n">
-        <v>975.5</v>
+        <v>0.9755</v>
       </c>
       <c r="Z41" t="n">
         <v>812.448</v>
@@ -8404,7 +8430,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="AG41" t="n">
-        <v>976.3</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="AH41" t="n">
         <v>798.148</v>
@@ -8574,7 +8600,7 @@
         <v>81.8</v>
       </c>
       <c r="Y42" t="n">
-        <v>969.3</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="Z42" t="n">
         <v>812.45</v>
@@ -8598,7 +8624,7 @@
         <v>82.7</v>
       </c>
       <c r="AG42" t="n">
-        <v>978.9</v>
+        <v>0.9789</v>
       </c>
       <c r="AH42" t="n">
         <v>798.15</v>
@@ -8768,7 +8794,7 @@
         <v>82.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>973.4</v>
+        <v>0.9734</v>
       </c>
       <c r="Z43" t="n">
         <v>812.451</v>
@@ -8792,7 +8818,7 @@
         <v>82.7</v>
       </c>
       <c r="AG43" t="n">
-        <v>979.9</v>
+        <v>0.9799</v>
       </c>
       <c r="AH43" t="n">
         <v>798.151</v>
@@ -8962,7 +8988,7 @@
         <v>82.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>976.7</v>
+        <v>0.9767</v>
       </c>
       <c r="Z44" t="n">
         <v>812.452</v>
@@ -8986,7 +9012,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="AG44" t="n">
-        <v>982.1</v>
+        <v>0.9821</v>
       </c>
       <c r="AH44" t="n">
         <v>798.152</v>
@@ -9156,7 +9182,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="Y45" t="n">
-        <v>975.8</v>
+        <v>0.9758</v>
       </c>
       <c r="Z45" t="n">
         <v>812.454</v>
@@ -9180,7 +9206,7 @@
         <v>83.2</v>
       </c>
       <c r="AG45" t="n">
-        <v>985</v>
+        <v>0.985</v>
       </c>
       <c r="AH45" t="n">
         <v>798.154</v>
@@ -9350,7 +9376,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="Y46" t="n">
-        <v>978.8</v>
+        <v>0.9788</v>
       </c>
       <c r="Z46" t="n">
         <v>812.455</v>
@@ -9374,7 +9400,7 @@
         <v>83.59999999999999</v>
       </c>
       <c r="AG46" t="n">
-        <v>990.3</v>
+        <v>0.9903</v>
       </c>
       <c r="AH46" t="n">
         <v>798.155</v>
@@ -9544,7 +9570,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="Y47" t="n">
-        <v>983.8</v>
+        <v>0.9838</v>
       </c>
       <c r="Z47" t="n">
         <v>812.456</v>
@@ -9568,7 +9594,7 @@
         <v>83.2</v>
       </c>
       <c r="AG47" t="n">
-        <v>985.1</v>
+        <v>0.9851</v>
       </c>
       <c r="AH47" t="n">
         <v>798.1559999999999</v>
@@ -9738,7 +9764,7 @@
         <v>82.7</v>
       </c>
       <c r="Y48" t="n">
-        <v>979.2</v>
+        <v>0.9792</v>
       </c>
       <c r="Z48" t="n">
         <v>812.458</v>
@@ -9762,7 +9788,7 @@
         <v>82.7</v>
       </c>
       <c r="AG48" t="n">
-        <v>979.1</v>
+        <v>0.9791</v>
       </c>
       <c r="AH48" t="n">
         <v>798.158</v>
@@ -9932,7 +9958,7 @@
         <v>82.3</v>
       </c>
       <c r="Y49" t="n">
-        <v>974.5</v>
+        <v>0.9745</v>
       </c>
       <c r="Z49" t="n">
         <v>812.4589999999999</v>
@@ -9956,7 +9982,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="AG49" t="n">
-        <v>984.3</v>
+        <v>0.9843</v>
       </c>
       <c r="AH49" t="n">
         <v>798.159</v>
@@ -10126,7 +10152,7 @@
         <v>82.5</v>
       </c>
       <c r="Y50" t="n">
-        <v>977.7</v>
+        <v>0.9777</v>
       </c>
       <c r="Z50" t="n">
         <v>812.46</v>
@@ -10150,7 +10176,7 @@
         <v>83.40000000000001</v>
       </c>
       <c r="AG50" t="n">
-        <v>988.1</v>
+        <v>0.9881</v>
       </c>
       <c r="AH50" t="n">
         <v>798.16</v>
@@ -10320,7 +10346,7 @@
         <v>82.2</v>
       </c>
       <c r="Y51" t="n">
-        <v>973.5</v>
+        <v>0.9735</v>
       </c>
       <c r="Z51" t="n">
         <v>812.462</v>
@@ -10344,7 +10370,7 @@
         <v>82.7</v>
       </c>
       <c r="AG51" t="n">
-        <v>979.2</v>
+        <v>0.9792</v>
       </c>
       <c r="AH51" t="n">
         <v>798.162</v>
@@ -10514,7 +10540,7 @@
         <v>82</v>
       </c>
       <c r="Y52" t="n">
-        <v>970.9</v>
+        <v>0.9709</v>
       </c>
       <c r="Z52" t="n">
         <v>812.463</v>
@@ -10538,7 +10564,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="AG52" t="n">
-        <v>984</v>
+        <v>0.984</v>
       </c>
       <c r="AH52" t="n">
         <v>798.163</v>
@@ -10708,7 +10734,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="Y53" t="n">
-        <v>969.4</v>
+        <v>0.9694</v>
       </c>
       <c r="Z53" t="n">
         <v>812.465</v>
@@ -10732,7 +10758,7 @@
         <v>83.2</v>
       </c>
       <c r="AG53" t="n">
-        <v>985.6</v>
+        <v>0.9856</v>
       </c>
       <c r="AH53" t="n">
         <v>798.165</v>
@@ -10902,7 +10928,7 @@
         <v>82</v>
       </c>
       <c r="Y54" t="n">
-        <v>970.8</v>
+        <v>0.9708</v>
       </c>
       <c r="Z54" t="n">
         <v>812.466</v>
@@ -10926,7 +10952,7 @@
         <v>83</v>
       </c>
       <c r="AG54" t="n">
-        <v>982.9</v>
+        <v>0.9829</v>
       </c>
       <c r="AH54" t="n">
         <v>798.1660000000001</v>
@@ -11096,7 +11122,7 @@
         <v>81.3</v>
       </c>
       <c r="Y55" t="n">
-        <v>963.1</v>
+        <v>0.9631</v>
       </c>
       <c r="Z55" t="n">
         <v>812.467</v>
@@ -11120,7 +11146,7 @@
         <v>82.3</v>
       </c>
       <c r="AG55" t="n">
-        <v>974.4</v>
+        <v>0.9744</v>
       </c>
       <c r="AH55" t="n">
         <v>798.167</v>
@@ -11290,7 +11316,7 @@
         <v>80.8</v>
       </c>
       <c r="Y56" t="n">
-        <v>956.8</v>
+        <v>0.9568</v>
       </c>
       <c r="Z56" t="n">
         <v>812.4690000000001</v>
@@ -11314,7 +11340,7 @@
         <v>82</v>
       </c>
       <c r="AG56" t="n">
-        <v>971.1</v>
+        <v>0.9711</v>
       </c>
       <c r="AH56" t="n">
         <v>798.169</v>
@@ -11484,7 +11510,7 @@
         <v>80.5</v>
       </c>
       <c r="Y57" t="n">
-        <v>953.8</v>
+        <v>0.9538</v>
       </c>
       <c r="Z57" t="n">
         <v>812.47</v>
@@ -11508,7 +11534,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG57" t="n">
-        <v>970</v>
+        <v>0.97</v>
       </c>
       <c r="AH57" t="n">
         <v>798.17</v>
@@ -11678,7 +11704,7 @@
         <v>80.09999999999999</v>
       </c>
       <c r="Y58" t="n">
-        <v>948.5</v>
+        <v>0.9485</v>
       </c>
       <c r="Z58" t="n">
         <v>812.471</v>
@@ -11702,7 +11728,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="AG58" t="n">
-        <v>963.7</v>
+        <v>0.9637</v>
       </c>
       <c r="AH58" t="n">
         <v>798.171</v>
@@ -11872,7 +11898,7 @@
         <v>80.3</v>
       </c>
       <c r="Y59" t="n">
-        <v>951.1</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="Z59" t="n">
         <v>812.473</v>
@@ -11896,7 +11922,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG59" t="n">
-        <v>970.6</v>
+        <v>0.9706</v>
       </c>
       <c r="AH59" t="n">
         <v>798.173</v>
@@ -12066,7 +12092,7 @@
         <v>80.8</v>
       </c>
       <c r="Y60" t="n">
-        <v>957.1</v>
+        <v>0.9571</v>
       </c>
       <c r="Z60" t="n">
         <v>812.474</v>
@@ -12090,7 +12116,7 @@
         <v>82.5</v>
       </c>
       <c r="AG60" t="n">
-        <v>977.4</v>
+        <v>0.9774</v>
       </c>
       <c r="AH60" t="n">
         <v>798.174</v>
@@ -12260,7 +12286,7 @@
         <v>80.7</v>
       </c>
       <c r="Y61" t="n">
-        <v>955.3</v>
+        <v>0.9553</v>
       </c>
       <c r="Z61" t="n">
         <v>812.475</v>
@@ -12284,7 +12310,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="AG61" t="n">
-        <v>976.2</v>
+        <v>0.9762</v>
       </c>
       <c r="AH61" t="n">
         <v>798.175</v>
@@ -12454,7 +12480,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="Y62" t="n">
-        <v>954.4</v>
+        <v>0.9544</v>
       </c>
       <c r="Z62" t="n">
         <v>812.477</v>
@@ -12478,7 +12504,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="AG62" t="n">
-        <v>981.9</v>
+        <v>0.9819</v>
       </c>
       <c r="AH62" t="n">
         <v>798.177</v>
@@ -12648,7 +12674,7 @@
         <v>80.3</v>
       </c>
       <c r="Y63" t="n">
-        <v>950.9</v>
+        <v>0.9509</v>
       </c>
       <c r="Z63" t="n">
         <v>812.478</v>
@@ -12672,7 +12698,7 @@
         <v>83</v>
       </c>
       <c r="AG63" t="n">
-        <v>982.7</v>
+        <v>0.9827</v>
       </c>
       <c r="AH63" t="n">
         <v>798.178</v>
@@ -12842,7 +12868,7 @@
         <v>80.40000000000001</v>
       </c>
       <c r="Y64" t="n">
-        <v>952.1</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="Z64" t="n">
         <v>812.479</v>
@@ -12866,7 +12892,7 @@
         <v>83.40000000000001</v>
       </c>
       <c r="AG64" t="n">
-        <v>987.7</v>
+        <v>0.9877</v>
       </c>
       <c r="AH64" t="n">
         <v>798.1799999999999</v>
@@ -13036,7 +13062,7 @@
         <v>80.3</v>
       </c>
       <c r="Y65" t="n">
-        <v>951</v>
+        <v>0.951</v>
       </c>
       <c r="Z65" t="n">
         <v>812.48</v>
@@ -13060,7 +13086,7 @@
         <v>83.59999999999999</v>
       </c>
       <c r="AG65" t="n">
-        <v>989.7</v>
+        <v>0.9897</v>
       </c>
       <c r="AH65" t="n">
         <v>798.181</v>
@@ -13230,7 +13256,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="Y66" t="n">
-        <v>954.2</v>
+        <v>0.9542</v>
       </c>
       <c r="Z66" t="n">
         <v>812.482</v>
@@ -13254,7 +13280,7 @@
         <v>83.3</v>
       </c>
       <c r="AG66" t="n">
-        <v>987.2</v>
+        <v>0.9872</v>
       </c>
       <c r="AH66" t="n">
         <v>798.182</v>
@@ -13424,7 +13450,7 @@
         <v>80.8</v>
       </c>
       <c r="Y67" t="n">
-        <v>957.4</v>
+        <v>0.9574</v>
       </c>
       <c r="Z67" t="n">
         <v>812.4829999999999</v>
@@ -13448,7 +13474,7 @@
         <v>83.5</v>
       </c>
       <c r="AG67" t="n">
-        <v>988.4</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="AH67" t="n">
         <v>798.184</v>
@@ -13618,7 +13644,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="Y68" t="n">
-        <v>957.7</v>
+        <v>0.9577</v>
       </c>
       <c r="Z68" t="n">
         <v>812.484</v>
@@ -13642,7 +13668,7 @@
         <v>83.3</v>
       </c>
       <c r="AG68" t="n">
-        <v>986.5</v>
+        <v>0.9865</v>
       </c>
       <c r="AH68" t="n">
         <v>798.1849999999999</v>
@@ -13812,7 +13838,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="Y69" t="n">
-        <v>960.3</v>
+        <v>0.9603</v>
       </c>
       <c r="Z69" t="n">
         <v>812.486</v>
@@ -13836,7 +13862,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="AG69" t="n">
-        <v>977.8</v>
+        <v>0.9778</v>
       </c>
       <c r="AH69" t="n">
         <v>798.186</v>
@@ -14006,7 +14032,7 @@
         <v>81.8</v>
       </c>
       <c r="Y70" t="n">
-        <v>968.3</v>
+        <v>0.9683</v>
       </c>
       <c r="Z70" t="n">
         <v>812.487</v>
@@ -14030,7 +14056,7 @@
         <v>82</v>
       </c>
       <c r="AG70" t="n">
-        <v>971.3</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="AH70" t="n">
         <v>798.188</v>
@@ -14200,7 +14226,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="Y71" t="n">
-        <v>966.1</v>
+        <v>0.9661</v>
       </c>
       <c r="Z71" t="n">
         <v>812.4880000000001</v>
@@ -14224,7 +14250,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG71" t="n">
-        <v>966.8</v>
+        <v>0.9668</v>
       </c>
       <c r="AH71" t="n">
         <v>798.189</v>
@@ -14394,7 +14420,7 @@
         <v>81.5</v>
       </c>
       <c r="Y72" t="n">
-        <v>964.7</v>
+        <v>0.9647</v>
       </c>
       <c r="Z72" t="n">
         <v>812.49</v>
@@ -14418,7 +14444,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG72" t="n">
-        <v>969.8</v>
+        <v>0.9698</v>
       </c>
       <c r="AH72" t="n">
         <v>798.1900000000001</v>
@@ -14588,7 +14614,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="Y73" t="n">
-        <v>958.1</v>
+        <v>0.9581</v>
       </c>
       <c r="Z73" t="n">
         <v>812.491</v>
@@ -14612,7 +14638,7 @@
         <v>82.3</v>
       </c>
       <c r="AG73" t="n">
-        <v>975.3</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="AH73" t="n">
         <v>798.192</v>
@@ -14782,7 +14808,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="Y74" t="n">
-        <v>964.4</v>
+        <v>0.9644</v>
       </c>
       <c r="Z74" t="n">
         <v>812.492</v>
@@ -14806,7 +14832,7 @@
         <v>82.7</v>
       </c>
       <c r="AG74" t="n">
-        <v>979.6</v>
+        <v>0.9796</v>
       </c>
       <c r="AH74" t="n">
         <v>798.193</v>
@@ -14976,7 +15002,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="Y75" t="n">
-        <v>958.5</v>
+        <v>0.9585</v>
       </c>
       <c r="Z75" t="n">
         <v>812.494</v>
@@ -15000,7 +15026,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="AG75" t="n">
-        <v>982.2</v>
+        <v>0.9822</v>
       </c>
       <c r="AH75" t="n">
         <v>798.194</v>
@@ -15170,7 +15196,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="Y76" t="n">
-        <v>960.5</v>
+        <v>0.9605</v>
       </c>
       <c r="Z76" t="n">
         <v>812.495</v>
@@ -15194,7 +15220,7 @@
         <v>82.5</v>
       </c>
       <c r="AG76" t="n">
-        <v>976.6</v>
+        <v>0.9766</v>
       </c>
       <c r="AH76" t="n">
         <v>798.196</v>
@@ -15364,7 +15390,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="Y77" t="n">
-        <v>964.3</v>
+        <v>0.9643</v>
       </c>
       <c r="Z77" t="n">
         <v>812.496</v>
@@ -15388,7 +15414,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG77" t="n">
-        <v>970.5</v>
+        <v>0.9705</v>
       </c>
       <c r="AH77" t="n">
         <v>798.197</v>
@@ -15558,7 +15584,7 @@
         <v>81.5</v>
       </c>
       <c r="Y78" t="n">
-        <v>965.6</v>
+        <v>0.9656</v>
       </c>
       <c r="Z78" t="n">
         <v>812.498</v>
@@ -15582,7 +15608,7 @@
         <v>82.3</v>
       </c>
       <c r="AG78" t="n">
-        <v>974.9</v>
+        <v>0.9749</v>
       </c>
       <c r="AH78" t="n">
         <v>798.199</v>
@@ -15752,7 +15778,7 @@
         <v>82</v>
       </c>
       <c r="Y79" t="n">
-        <v>970.8</v>
+        <v>0.9708</v>
       </c>
       <c r="Z79" t="n">
         <v>812.499</v>
@@ -15776,7 +15802,7 @@
         <v>82.5</v>
       </c>
       <c r="AG79" t="n">
-        <v>977.6</v>
+        <v>0.9776</v>
       </c>
       <c r="AH79" t="n">
         <v>798.2</v>
@@ -15946,7 +15972,7 @@
         <v>82.5</v>
       </c>
       <c r="Y80" t="n">
-        <v>976.5</v>
+        <v>0.9765</v>
       </c>
       <c r="Z80" t="n">
         <v>812.501</v>
@@ -15970,7 +15996,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="AG80" t="n">
-        <v>983.9</v>
+        <v>0.9839</v>
       </c>
       <c r="AH80" t="n">
         <v>798.201</v>
@@ -16140,7 +16166,7 @@
         <v>82</v>
       </c>
       <c r="Y81" t="n">
-        <v>970.7</v>
+        <v>0.9707</v>
       </c>
       <c r="Z81" t="n">
         <v>812.502</v>
@@ -16164,7 +16190,7 @@
         <v>83</v>
       </c>
       <c r="AG81" t="n">
-        <v>983.2</v>
+        <v>0.9832</v>
       </c>
       <c r="AH81" t="n">
         <v>798.203</v>
@@ -16334,7 +16360,7 @@
         <v>81.5</v>
       </c>
       <c r="Y82" t="n">
-        <v>965.6</v>
+        <v>0.9656</v>
       </c>
       <c r="Z82" t="n">
         <v>812.503</v>
@@ -16358,7 +16384,7 @@
         <v>82.7</v>
       </c>
       <c r="AG82" t="n">
-        <v>979.2</v>
+        <v>0.9792</v>
       </c>
       <c r="AH82" t="n">
         <v>798.204</v>
@@ -16528,7 +16554,7 @@
         <v>82</v>
       </c>
       <c r="Y83" t="n">
-        <v>970.8</v>
+        <v>0.9708</v>
       </c>
       <c r="Z83" t="n">
         <v>812.505</v>
@@ -16552,7 +16578,7 @@
         <v>83.2</v>
       </c>
       <c r="AG83" t="n">
-        <v>984.9</v>
+        <v>0.9849</v>
       </c>
       <c r="AH83" t="n">
         <v>798.205</v>
@@ -16722,7 +16748,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="Y84" t="n">
-        <v>972.2</v>
+        <v>0.9722</v>
       </c>
       <c r="Z84" t="n">
         <v>812.506</v>
@@ -16746,7 +16772,7 @@
         <v>83</v>
       </c>
       <c r="AG84" t="n">
-        <v>983.1</v>
+        <v>0.9831</v>
       </c>
       <c r="AH84" t="n">
         <v>798.207</v>
@@ -16916,7 +16942,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="Y85" t="n">
-        <v>975.6</v>
+        <v>0.9756</v>
       </c>
       <c r="Z85" t="n">
         <v>812.5069999999999</v>
@@ -16940,7 +16966,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="AG85" t="n">
-        <v>983.8</v>
+        <v>0.9838</v>
       </c>
       <c r="AH85" t="n">
         <v>798.208</v>
@@ -17110,7 +17136,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="Y86" t="n">
-        <v>975.8</v>
+        <v>0.9758</v>
       </c>
       <c r="Z86" t="n">
         <v>812.509</v>
@@ -17134,7 +17160,7 @@
         <v>83.59999999999999</v>
       </c>
       <c r="AG86" t="n">
-        <v>989.7</v>
+        <v>0.9897</v>
       </c>
       <c r="AH86" t="n">
         <v>798.2089999999999</v>
@@ -17304,7 +17330,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="Y87" t="n">
-        <v>972.4</v>
+        <v>0.9724</v>
       </c>
       <c r="Z87" t="n">
         <v>812.51</v>
@@ -17328,7 +17354,7 @@
         <v>83.3</v>
       </c>
       <c r="AG87" t="n">
-        <v>986.6</v>
+        <v>0.9866</v>
       </c>
       <c r="AH87" t="n">
         <v>798.211</v>
@@ -17498,7 +17524,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="Y88" t="n">
-        <v>972.5</v>
+        <v>0.9725</v>
       </c>
       <c r="Z88" t="n">
         <v>812.511</v>
@@ -17522,7 +17548,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="AG88" t="n">
-        <v>978.6</v>
+        <v>0.9786</v>
       </c>
       <c r="AH88" t="n">
         <v>798.212</v>
@@ -17692,7 +17718,7 @@
         <v>81.5</v>
       </c>
       <c r="Y89" t="n">
-        <v>965.7</v>
+        <v>0.9657</v>
       </c>
       <c r="Z89" t="n">
         <v>812.513</v>
@@ -17716,7 +17742,7 @@
         <v>82.5</v>
       </c>
       <c r="AG89" t="n">
-        <v>977</v>
+        <v>0.977</v>
       </c>
       <c r="AH89" t="n">
         <v>798.2140000000001</v>
@@ -17886,7 +17912,7 @@
         <v>81</v>
       </c>
       <c r="Y90" t="n">
-        <v>959.5</v>
+        <v>0.9595</v>
       </c>
       <c r="Z90" t="n">
         <v>812.514</v>
@@ -17910,7 +17936,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="AG90" t="n">
-        <v>978</v>
+        <v>0.978</v>
       </c>
       <c r="AH90" t="n">
         <v>798.215</v>
@@ -18080,7 +18106,7 @@
         <v>81</v>
       </c>
       <c r="Y91" t="n">
-        <v>959.5</v>
+        <v>0.9595</v>
       </c>
       <c r="Z91" t="n">
         <v>812.515</v>
@@ -18104,7 +18130,7 @@
         <v>82.5</v>
       </c>
       <c r="AG91" t="n">
-        <v>977</v>
+        <v>0.977</v>
       </c>
       <c r="AH91" t="n">
         <v>798.216</v>
@@ -18274,7 +18300,7 @@
         <v>81.2</v>
       </c>
       <c r="Y92" t="n">
-        <v>962.3</v>
+        <v>0.9623</v>
       </c>
       <c r="Z92" t="n">
         <v>812.5170000000001</v>
@@ -18298,7 +18324,7 @@
         <v>82.5</v>
       </c>
       <c r="AG92" t="n">
-        <v>977.7</v>
+        <v>0.9777</v>
       </c>
       <c r="AH92" t="n">
         <v>798.218</v>
@@ -18468,7 +18494,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="Y93" t="n">
-        <v>969.7</v>
+        <v>0.9697</v>
       </c>
       <c r="Z93" t="n">
         <v>812.518</v>
@@ -18492,7 +18518,7 @@
         <v>82.2</v>
       </c>
       <c r="AG93" t="n">
-        <v>973.4</v>
+        <v>0.9734</v>
       </c>
       <c r="AH93" t="n">
         <v>798.2190000000001</v>
@@ -18662,7 +18688,7 @@
         <v>81.3</v>
       </c>
       <c r="Y94" t="n">
-        <v>963.3</v>
+        <v>0.9633</v>
       </c>
       <c r="Z94" t="n">
         <v>812.519</v>
@@ -18686,7 +18712,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="AG94" t="n">
-        <v>978.2</v>
+        <v>0.9782</v>
       </c>
       <c r="AH94" t="n">
         <v>798.22</v>
@@ -18856,7 +18882,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="Y95" t="n">
-        <v>958.7</v>
+        <v>0.9587</v>
       </c>
       <c r="Z95" t="n">
         <v>812.521</v>
@@ -18880,7 +18906,7 @@
         <v>83</v>
       </c>
       <c r="AG95" t="n">
-        <v>982.5</v>
+        <v>0.9825</v>
       </c>
       <c r="AH95" t="n">
         <v>798.222</v>
@@ -19050,7 +19076,7 @@
         <v>80.5</v>
       </c>
       <c r="Y96" t="n">
-        <v>953.7</v>
+        <v>0.9537</v>
       </c>
       <c r="Z96" t="n">
         <v>812.522</v>
@@ -19074,7 +19100,7 @@
         <v>83.2</v>
       </c>
       <c r="AG96" t="n">
-        <v>985</v>
+        <v>0.985</v>
       </c>
       <c r="AH96" t="n">
         <v>798.223</v>
@@ -19244,7 +19270,7 @@
         <v>81</v>
       </c>
       <c r="Y97" t="n">
-        <v>959.1</v>
+        <v>0.9591</v>
       </c>
       <c r="Z97" t="n">
         <v>812.523</v>
@@ -19268,7 +19294,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="AG97" t="n">
-        <v>976.3</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="AH97" t="n">
         <v>798.224</v>
@@ -19438,7 +19464,7 @@
         <v>81.5</v>
       </c>
       <c r="Y98" t="n">
-        <v>965.8</v>
+        <v>0.9658</v>
       </c>
       <c r="Z98" t="n">
         <v>812.525</v>
@@ -19462,7 +19488,7 @@
         <v>82</v>
       </c>
       <c r="AG98" t="n">
-        <v>971.7</v>
+        <v>0.9717</v>
       </c>
       <c r="AH98" t="n">
         <v>798.226</v>
@@ -19632,7 +19658,7 @@
         <v>81.7</v>
       </c>
       <c r="Y99" t="n">
-        <v>967.9</v>
+        <v>0.9679</v>
       </c>
       <c r="Z99" t="n">
         <v>812.526</v>
@@ -19656,7 +19682,7 @@
         <v>82</v>
       </c>
       <c r="AG99" t="n">
-        <v>971</v>
+        <v>0.971</v>
       </c>
       <c r="AH99" t="n">
         <v>798.227</v>
@@ -19826,7 +19852,7 @@
         <v>81.7</v>
       </c>
       <c r="Y100" t="n">
-        <v>967.6</v>
+        <v>0.9676</v>
       </c>
       <c r="Z100" t="n">
         <v>812.527</v>
@@ -19850,7 +19876,7 @@
         <v>82.5</v>
       </c>
       <c r="AG100" t="n">
-        <v>976.9</v>
+        <v>0.9769</v>
       </c>
       <c r="AH100" t="n">
         <v>798.228</v>
@@ -20020,7 +20046,7 @@
         <v>82.2</v>
       </c>
       <c r="Y101" t="n">
-        <v>973.1</v>
+        <v>0.9731</v>
       </c>
       <c r="Z101" t="n">
         <v>812.529</v>
@@ -20044,7 +20070,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="AG101" t="n">
-        <v>982.4</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="AH101" t="n">
         <v>798.23</v>
@@ -20214,7 +20240,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="Y102" t="n">
-        <v>970.3</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="Z102" t="n">
         <v>812.53</v>
@@ -20238,7 +20264,7 @@
         <v>83.5</v>
       </c>
       <c r="AG102" t="n">
-        <v>988.4</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="AH102" t="n">
         <v>798.231</v>
@@ -20408,7 +20434,7 @@
         <v>82</v>
       </c>
       <c r="Y103" t="n">
-        <v>971.5</v>
+        <v>0.9715</v>
       </c>
       <c r="Z103" t="n">
         <v>812.5309999999999</v>
@@ -20432,7 +20458,7 @@
         <v>82.8</v>
       </c>
       <c r="AG103" t="n">
-        <v>980.2</v>
+        <v>0.9802</v>
       </c>
       <c r="AH103" t="n">
         <v>798.2329999999999</v>
@@ -20602,7 +20628,7 @@
         <v>82</v>
       </c>
       <c r="Y104" t="n">
-        <v>971.3</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="Z104" t="n">
         <v>812.533</v>
@@ -20626,7 +20652,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="AG104" t="n">
-        <v>984.4</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="AH104" t="n">
         <v>798.234</v>
@@ -20796,7 +20822,7 @@
         <v>81.5</v>
       </c>
       <c r="Y105" t="n">
-        <v>965.9</v>
+        <v>0.9659</v>
       </c>
       <c r="Z105" t="n">
         <v>812.534</v>
@@ -20820,7 +20846,7 @@
         <v>83.40000000000001</v>
       </c>
       <c r="AG105" t="n">
-        <v>987.5</v>
+        <v>0.9875</v>
       </c>
       <c r="AH105" t="n">
         <v>798.235</v>
@@ -20990,7 +21016,7 @@
         <v>81</v>
       </c>
       <c r="Y106" t="n">
-        <v>959.8</v>
+        <v>0.9598</v>
       </c>
       <c r="Z106" t="n">
         <v>812.535</v>
@@ -21014,7 +21040,7 @@
         <v>83.40000000000001</v>
       </c>
       <c r="AG106" t="n">
-        <v>987.8</v>
+        <v>0.9878</v>
       </c>
       <c r="AH106" t="n">
         <v>798.237</v>
@@ -21184,7 +21210,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="Y107" t="n">
-        <v>954.9</v>
+        <v>0.9549</v>
       </c>
       <c r="Z107" t="n">
         <v>812.537</v>
@@ -21208,7 +21234,7 @@
         <v>83.59999999999999</v>
       </c>
       <c r="AG107" t="n">
-        <v>990.7</v>
+        <v>0.9907</v>
       </c>
       <c r="AH107" t="n">
         <v>798.2380000000001</v>
@@ -21378,7 +21404,7 @@
         <v>81</v>
       </c>
       <c r="Y108" t="n">
-        <v>959.4</v>
+        <v>0.9594</v>
       </c>
       <c r="Z108" t="n">
         <v>812.538</v>
@@ -21402,7 +21428,7 @@
         <v>83.40000000000001</v>
       </c>
       <c r="AG108" t="n">
-        <v>988</v>
+        <v>0.988</v>
       </c>
       <c r="AH108" t="n">
         <v>798.239</v>
@@ -21572,7 +21598,7 @@
         <v>80.8</v>
       </c>
       <c r="Y109" t="n">
-        <v>957.3</v>
+        <v>0.9573</v>
       </c>
       <c r="Z109" t="n">
         <v>812.539</v>
@@ -21596,7 +21622,7 @@
         <v>83.7</v>
       </c>
       <c r="AG109" t="n">
-        <v>991.5</v>
+        <v>0.9915</v>
       </c>
       <c r="AH109" t="n">
         <v>798.241</v>
@@ -21766,7 +21792,7 @@
         <v>80.7</v>
       </c>
       <c r="Y110" t="n">
-        <v>955.6</v>
+        <v>0.9556</v>
       </c>
       <c r="Z110" t="n">
         <v>812.5410000000001</v>
@@ -21790,7 +21816,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="AG110" t="n">
-        <v>982.3</v>
+        <v>0.9823</v>
       </c>
       <c r="AH110" t="n">
         <v>798.242</v>
@@ -21960,7 +21986,7 @@
         <v>80.5</v>
       </c>
       <c r="Y111" t="n">
-        <v>952.9</v>
+        <v>0.9529</v>
       </c>
       <c r="Z111" t="n">
         <v>812.542</v>
@@ -21984,7 +22010,7 @@
         <v>83.40000000000001</v>
       </c>
       <c r="AG111" t="n">
-        <v>988.3</v>
+        <v>0.9883</v>
       </c>
       <c r="AH111" t="n">
         <v>798.244</v>
@@ -22154,7 +22180,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="Y112" t="n">
-        <v>960.8</v>
+        <v>0.9608</v>
       </c>
       <c r="Z112" t="n">
         <v>812.543</v>
@@ -22178,7 +22204,7 @@
         <v>83</v>
       </c>
       <c r="AG112" t="n">
-        <v>982.7</v>
+        <v>0.9827</v>
       </c>
       <c r="AH112" t="n">
         <v>798.245</v>
@@ -22348,7 +22374,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="Y113" t="n">
-        <v>965.9</v>
+        <v>0.9659</v>
       </c>
       <c r="Z113" t="n">
         <v>812.545</v>
@@ -22372,7 +22398,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="AG113" t="n">
-        <v>981.8</v>
+        <v>0.9818</v>
       </c>
       <c r="AH113" t="n">
         <v>798.246</v>
@@ -22542,7 +22568,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="Y114" t="n">
-        <v>969.8</v>
+        <v>0.9698</v>
       </c>
       <c r="Z114" t="n">
         <v>812.546</v>
@@ -22566,7 +22592,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="AG114" t="n">
-        <v>975.9</v>
+        <v>0.9759</v>
       </c>
       <c r="AH114" t="n">
         <v>798.248</v>
@@ -22736,7 +22762,7 @@
         <v>81.7</v>
       </c>
       <c r="Y115" t="n">
-        <v>967.2</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="Z115" t="n">
         <v>812.547</v>
@@ -22760,7 +22786,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG115" t="n">
-        <v>969.9</v>
+        <v>0.9699</v>
       </c>
       <c r="AH115" t="n">
         <v>798.249</v>
@@ -22930,7 +22956,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="Y116" t="n">
-        <v>972.3</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="Z116" t="n">
         <v>812.549</v>
@@ -22954,7 +22980,7 @@
         <v>82</v>
       </c>
       <c r="AG116" t="n">
-        <v>971.1</v>
+        <v>0.9711</v>
       </c>
       <c r="AH116" t="n">
         <v>798.25</v>
@@ -23124,7 +23150,7 @@
         <v>82.5</v>
       </c>
       <c r="Y117" t="n">
-        <v>977.4</v>
+        <v>0.9774</v>
       </c>
       <c r="Z117" t="n">
         <v>812.55</v>
@@ -23148,7 +23174,7 @@
         <v>81.7</v>
       </c>
       <c r="AG117" t="n">
-        <v>967.1</v>
+        <v>0.9671</v>
       </c>
       <c r="AH117" t="n">
         <v>798.252</v>
@@ -23318,7 +23344,7 @@
         <v>82.2</v>
       </c>
       <c r="Y118" t="n">
-        <v>973.9</v>
+        <v>0.9739</v>
       </c>
       <c r="Z118" t="n">
         <v>812.552</v>
@@ -23342,7 +23368,7 @@
         <v>82.2</v>
       </c>
       <c r="AG118" t="n">
-        <v>974.1</v>
+        <v>0.9741</v>
       </c>
       <c r="AH118" t="n">
         <v>798.253</v>
@@ -23512,7 +23538,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="Y119" t="n">
-        <v>975.9</v>
+        <v>0.9759</v>
       </c>
       <c r="Z119" t="n">
         <v>812.553</v>
@@ -23536,7 +23562,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG119" t="n">
-        <v>969.8</v>
+        <v>0.9698</v>
       </c>
       <c r="AH119" t="n">
         <v>798.254</v>
@@ -23706,7 +23732,7 @@
         <v>81.7</v>
       </c>
       <c r="Y120" t="n">
-        <v>968.2</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="Z120" t="n">
         <v>812.554</v>
@@ -23730,7 +23756,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG120" t="n">
-        <v>966.2</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="AH120" t="n">
         <v>798.256</v>
@@ -23900,7 +23926,7 @@
         <v>81.2</v>
       </c>
       <c r="Y121" t="n">
-        <v>961.3</v>
+        <v>0.9613</v>
       </c>
       <c r="Z121" t="n">
         <v>812.556</v>
@@ -23924,7 +23950,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="AG121" t="n">
-        <v>972.8</v>
+        <v>0.9728</v>
       </c>
       <c r="AH121" t="n">
         <v>798.2569999999999</v>
@@ -24094,7 +24120,7 @@
         <v>81.2</v>
       </c>
       <c r="Y122" t="n">
-        <v>961.3</v>
+        <v>0.9613</v>
       </c>
       <c r="Z122" t="n">
         <v>812.557</v>
@@ -24118,7 +24144,7 @@
         <v>82.3</v>
       </c>
       <c r="AG122" t="n">
-        <v>975.2</v>
+        <v>0.9752</v>
       </c>
       <c r="AH122" t="n">
         <v>798.258</v>
@@ -24288,7 +24314,7 @@
         <v>81.8</v>
       </c>
       <c r="Y123" t="n">
-        <v>968.6</v>
+        <v>0.9686</v>
       </c>
       <c r="Z123" t="n">
         <v>812.558</v>
@@ -24312,7 +24338,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG123" t="n">
-        <v>969.6</v>
+        <v>0.9696</v>
       </c>
       <c r="AH123" t="n">
         <v>798.26</v>
@@ -24482,7 +24508,7 @@
         <v>81.7</v>
       </c>
       <c r="Y124" t="n">
-        <v>967.4</v>
+        <v>0.9674</v>
       </c>
       <c r="Z124" t="n">
         <v>812.5599999999999</v>
@@ -24506,7 +24532,7 @@
         <v>82</v>
       </c>
       <c r="AG124" t="n">
-        <v>971.4</v>
+        <v>0.9714</v>
       </c>
       <c r="AH124" t="n">
         <v>798.261</v>
@@ -24676,7 +24702,7 @@
         <v>81.2</v>
       </c>
       <c r="Y125" t="n">
-        <v>961.6</v>
+        <v>0.9616</v>
       </c>
       <c r="Z125" t="n">
         <v>812.561</v>
@@ -24700,7 +24726,7 @@
         <v>82.5</v>
       </c>
       <c r="AG125" t="n">
-        <v>977.1</v>
+        <v>0.9771</v>
       </c>
       <c r="AH125" t="n">
         <v>798.2619999999999</v>
@@ -24870,7 +24896,7 @@
         <v>81.5</v>
       </c>
       <c r="Y126" t="n">
-        <v>964.7</v>
+        <v>0.9647</v>
       </c>
       <c r="Z126" t="n">
         <v>812.562</v>
@@ -24894,7 +24920,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="AG126" t="n">
-        <v>972.5</v>
+        <v>0.9725</v>
       </c>
       <c r="AH126" t="n">
         <v>798.264</v>
@@ -25064,7 +25090,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="Y127" t="n">
-        <v>972.2</v>
+        <v>0.9722</v>
       </c>
       <c r="Z127" t="n">
         <v>812.564</v>
@@ -25088,7 +25114,7 @@
         <v>82.3</v>
       </c>
       <c r="AG127" t="n">
-        <v>975</v>
+        <v>0.975</v>
       </c>
       <c r="AH127" t="n">
         <v>798.265</v>
@@ -25258,7 +25284,7 @@
         <v>82.3</v>
       </c>
       <c r="Y128" t="n">
-        <v>974.3</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="Z128" t="n">
         <v>812.5650000000001</v>
@@ -25282,7 +25308,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG128" t="n">
-        <v>969.5</v>
+        <v>0.9695</v>
       </c>
       <c r="AH128" t="n">
         <v>798.2670000000001</v>
@@ -25452,7 +25478,7 @@
         <v>82.2</v>
       </c>
       <c r="Y129" t="n">
-        <v>973.1</v>
+        <v>0.9731</v>
       </c>
       <c r="Z129" t="n">
         <v>812.566</v>
@@ -25476,7 +25502,7 @@
         <v>82</v>
       </c>
       <c r="AG129" t="n">
-        <v>971.2</v>
+        <v>0.9712</v>
       </c>
       <c r="AH129" t="n">
         <v>798.268</v>
@@ -25646,7 +25672,7 @@
         <v>81.8</v>
       </c>
       <c r="Y130" t="n">
-        <v>968.6</v>
+        <v>0.9686</v>
       </c>
       <c r="Z130" t="n">
         <v>812.568</v>
@@ -25670,7 +25696,7 @@
         <v>82.5</v>
       </c>
       <c r="AG130" t="n">
-        <v>976.8</v>
+        <v>0.9768</v>
       </c>
       <c r="AH130" t="n">
         <v>798.269</v>
@@ -25840,7 +25866,7 @@
         <v>82.2</v>
       </c>
       <c r="Y131" t="n">
-        <v>973.3</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="Z131" t="n">
         <v>812.569</v>
@@ -25864,7 +25890,7 @@
         <v>82.5</v>
       </c>
       <c r="AG131" t="n">
-        <v>977.5</v>
+        <v>0.9775</v>
       </c>
       <c r="AH131" t="n">
         <v>798.271</v>
@@ -26034,7 +26060,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="Y132" t="n">
-        <v>978.4</v>
+        <v>0.9784</v>
       </c>
       <c r="Z132" t="n">
         <v>812.5700000000001</v>
@@ -26058,7 +26084,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="AG132" t="n">
-        <v>972.5</v>
+        <v>0.9725</v>
       </c>
       <c r="AH132" t="n">
         <v>798.272</v>
@@ -26228,7 +26254,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="Y133" t="n">
-        <v>975.4</v>
+        <v>0.9754</v>
       </c>
       <c r="Z133" t="n">
         <v>812.572</v>
@@ -26252,7 +26278,7 @@
         <v>81.8</v>
       </c>
       <c r="AG133" t="n">
-        <v>969.3</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="AH133" t="n">
         <v>798.273</v>
@@ -26422,7 +26448,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="Y134" t="n">
-        <v>978.1</v>
+        <v>0.9781</v>
       </c>
       <c r="Z134" t="n">
         <v>812.573</v>
@@ -26446,7 +26472,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG134" t="n">
-        <v>966</v>
+        <v>0.966</v>
       </c>
       <c r="AH134" t="n">
         <v>798.275</v>
@@ -26616,7 +26642,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="Y135" t="n">
-        <v>978.9</v>
+        <v>0.9789</v>
       </c>
       <c r="Z135" t="n">
         <v>812.574</v>
@@ -26640,7 +26666,7 @@
         <v>81.7</v>
       </c>
       <c r="AG135" t="n">
-        <v>967.1</v>
+        <v>0.9671</v>
       </c>
       <c r="AH135" t="n">
         <v>798.276</v>
@@ -26810,7 +26836,7 @@
         <v>82.7</v>
       </c>
       <c r="Y136" t="n">
-        <v>979.1</v>
+        <v>0.9791</v>
       </c>
       <c r="Z136" t="n">
         <v>812.576</v>
@@ -26834,7 +26860,7 @@
         <v>81.8</v>
       </c>
       <c r="AG136" t="n">
-        <v>968.3</v>
+        <v>0.9683</v>
       </c>
       <c r="AH136" t="n">
         <v>798.277</v>
@@ -27004,7 +27030,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="Y137" t="n">
-        <v>972.2</v>
+        <v>0.9722</v>
       </c>
       <c r="Z137" t="n">
         <v>812.577</v>
@@ -27028,7 +27054,7 @@
         <v>81.7</v>
       </c>
       <c r="AG137" t="n">
-        <v>967.1</v>
+        <v>0.9671</v>
       </c>
       <c r="AH137" t="n">
         <v>798.279</v>
@@ -27198,7 +27224,7 @@
         <v>81.8</v>
       </c>
       <c r="Y138" t="n">
-        <v>969.4</v>
+        <v>0.9694</v>
       </c>
       <c r="Z138" t="n">
         <v>812.578</v>
@@ -27222,7 +27248,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="AG138" t="n">
-        <v>971.9</v>
+        <v>0.9719</v>
       </c>
       <c r="AH138" t="n">
         <v>798.28</v>
@@ -27392,7 +27418,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="Y139" t="n">
-        <v>964.6</v>
+        <v>0.9646</v>
       </c>
       <c r="Z139" t="n">
         <v>812.58</v>
@@ -27416,7 +27442,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="AG139" t="n">
-        <v>977.9</v>
+        <v>0.9779</v>
       </c>
       <c r="AH139" t="n">
         <v>798.2809999999999</v>
@@ -27586,7 +27612,7 @@
         <v>82</v>
       </c>
       <c r="Y140" t="n">
-        <v>970.7</v>
+        <v>0.9707</v>
       </c>
       <c r="Z140" t="n">
         <v>812.581</v>
@@ -27610,7 +27636,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="AG140" t="n">
-        <v>981.4</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="AH140" t="n">
         <v>798.283</v>
@@ -27780,7 +27806,7 @@
         <v>82.3</v>
       </c>
       <c r="Y141" t="n">
-        <v>974.5</v>
+        <v>0.9745</v>
       </c>
       <c r="Z141" t="n">
         <v>812.583</v>
@@ -27804,7 +27830,7 @@
         <v>82.5</v>
       </c>
       <c r="AG141" t="n">
-        <v>977</v>
+        <v>0.977</v>
       </c>
       <c r="AH141" t="n">
         <v>798.284</v>
@@ -27974,7 +28000,7 @@
         <v>82.5</v>
       </c>
       <c r="Y142" t="n">
-        <v>977.3</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="Z142" t="n">
         <v>812.5839999999999</v>
@@ -27998,7 +28024,7 @@
         <v>82.8</v>
       </c>
       <c r="AG142" t="n">
-        <v>980.5</v>
+        <v>0.9805</v>
       </c>
       <c r="AH142" t="n">
         <v>798.285</v>
@@ -28168,7 +28194,7 @@
         <v>83</v>
       </c>
       <c r="Y143" t="n">
-        <v>982.8</v>
+        <v>0.9828</v>
       </c>
       <c r="Z143" t="n">
         <v>812.585</v>
@@ -28192,7 +28218,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="AG143" t="n">
-        <v>984.5</v>
+        <v>0.9845</v>
       </c>
       <c r="AH143" t="n">
         <v>798.287</v>
@@ -28362,7 +28388,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="Y144" t="n">
-        <v>984.1</v>
+        <v>0.9841</v>
       </c>
       <c r="Z144" t="n">
         <v>812.587</v>
@@ -28386,7 +28412,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="AG144" t="n">
-        <v>978.7</v>
+        <v>0.9787</v>
       </c>
       <c r="AH144" t="n">
         <v>798.288</v>
@@ -28556,7 +28582,7 @@
         <v>83.3</v>
       </c>
       <c r="Y145" t="n">
-        <v>986.4</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="Z145" t="n">
         <v>812.588</v>
@@ -28580,7 +28606,7 @@
         <v>82.3</v>
       </c>
       <c r="AG145" t="n">
-        <v>975.2</v>
+        <v>0.9752</v>
       </c>
       <c r="AH145" t="n">
         <v>798.29</v>
@@ -28750,7 +28776,7 @@
         <v>83.8</v>
       </c>
       <c r="Y146" t="n">
-        <v>992.2</v>
+        <v>0.9922</v>
       </c>
       <c r="Z146" t="n">
         <v>812.5890000000001</v>
@@ -28774,7 +28800,7 @@
         <v>82.5</v>
       </c>
       <c r="AG146" t="n">
-        <v>976.5</v>
+        <v>0.9765</v>
       </c>
       <c r="AH146" t="n">
         <v>798.2910000000001</v>
@@ -28944,7 +28970,7 @@
         <v>83.5</v>
       </c>
       <c r="Y147" t="n">
-        <v>989.5</v>
+        <v>0.9895</v>
       </c>
       <c r="Z147" t="n">
         <v>812.591</v>
@@ -28968,7 +28994,7 @@
         <v>83</v>
       </c>
       <c r="AG147" t="n">
-        <v>982.6</v>
+        <v>0.9826</v>
       </c>
       <c r="AH147" t="n">
         <v>798.292</v>
@@ -29138,7 +29164,7 @@
         <v>83.7</v>
       </c>
       <c r="Y148" t="n">
-        <v>991.8</v>
+        <v>0.9918</v>
       </c>
       <c r="Z148" t="n">
         <v>812.592</v>
@@ -29162,7 +29188,7 @@
         <v>82.8</v>
       </c>
       <c r="AG148" t="n">
-        <v>981.3</v>
+        <v>0.9813</v>
       </c>
       <c r="AH148" t="n">
         <v>798.294</v>
@@ -29332,7 +29358,7 @@
         <v>83.40000000000001</v>
       </c>
       <c r="Y149" t="n">
-        <v>987.6</v>
+        <v>0.9876</v>
       </c>
       <c r="Z149" t="n">
         <v>812.593</v>
@@ -29356,7 +29382,7 @@
         <v>82.5</v>
       </c>
       <c r="AG149" t="n">
-        <v>977.5</v>
+        <v>0.9775</v>
       </c>
       <c r="AH149" t="n">
         <v>798.295</v>
@@ -29526,7 +29552,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="Y150" t="n">
-        <v>983.8</v>
+        <v>0.9838</v>
       </c>
       <c r="Z150" t="n">
         <v>812.595</v>
@@ -29550,7 +29576,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="AG150" t="n">
-        <v>975.7</v>
+        <v>0.9757</v>
       </c>
       <c r="AH150" t="n">
         <v>798.296</v>
@@ -29720,7 +29746,7 @@
         <v>82.8</v>
       </c>
       <c r="Y151" t="n">
-        <v>980.5</v>
+        <v>0.9805</v>
       </c>
       <c r="Z151" t="n">
         <v>812.596</v>
@@ -29744,7 +29770,7 @@
         <v>82.5</v>
       </c>
       <c r="AG151" t="n">
-        <v>977</v>
+        <v>0.977</v>
       </c>
       <c r="AH151" t="n">
         <v>798.298</v>
@@ -29914,7 +29940,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="Y152" t="n">
-        <v>978.2</v>
+        <v>0.9782</v>
       </c>
       <c r="Z152" t="n">
         <v>812.598</v>
@@ -29938,7 +29964,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="AG152" t="n">
-        <v>983.7</v>
+        <v>0.9837</v>
       </c>
       <c r="AH152" t="n">
         <v>798.299</v>
@@ -30108,7 +30134,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="Y153" t="n">
-        <v>972</v>
+        <v>0.972</v>
       </c>
       <c r="Z153" t="n">
         <v>812.599</v>
@@ -30132,7 +30158,7 @@
         <v>83</v>
       </c>
       <c r="AG153" t="n">
-        <v>983.3</v>
+        <v>0.9833</v>
       </c>
       <c r="AH153" t="n">
         <v>798.3</v>
@@ -30302,7 +30328,7 @@
         <v>81.5</v>
       </c>
       <c r="Y154" t="n">
-        <v>965</v>
+        <v>0.965</v>
       </c>
       <c r="Z154" t="n">
         <v>812.6</v>
@@ -30326,7 +30352,7 @@
         <v>83.40000000000001</v>
       </c>
       <c r="AG154" t="n">
-        <v>988.3</v>
+        <v>0.9883</v>
       </c>
       <c r="AH154" t="n">
         <v>798.302</v>
@@ -30496,7 +30522,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="Y155" t="n">
-        <v>964.3</v>
+        <v>0.9643</v>
       </c>
       <c r="Z155" t="n">
         <v>812.602</v>
@@ -30520,7 +30546,7 @@
         <v>83.90000000000001</v>
       </c>
       <c r="AG155" t="n">
-        <v>993.3</v>
+        <v>0.9933</v>
       </c>
       <c r="AH155" t="n">
         <v>798.303</v>
@@ -30690,7 +30716,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="Y156" t="n">
-        <v>966.8</v>
+        <v>0.9668</v>
       </c>
       <c r="Z156" t="n">
         <v>812.603</v>
@@ -30714,7 +30740,7 @@
         <v>84.3</v>
       </c>
       <c r="AG156" t="n">
-        <v>998.6</v>
+        <v>0.9986</v>
       </c>
       <c r="AH156" t="n">
         <v>798.3049999999999</v>
@@ -30884,7 +30910,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="Y157" t="n">
-        <v>966.7</v>
+        <v>0.9667</v>
       </c>
       <c r="Z157" t="n">
         <v>812.604</v>
@@ -30908,7 +30934,7 @@
         <v>83.90000000000001</v>
       </c>
       <c r="AG157" t="n">
-        <v>993.2</v>
+        <v>0.9932</v>
       </c>
       <c r="AH157" t="n">
         <v>798.306</v>
@@ -31078,7 +31104,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="Y158" t="n">
-        <v>966.4</v>
+        <v>0.9664</v>
       </c>
       <c r="Z158" t="n">
         <v>812.606</v>
@@ -31102,7 +31128,7 @@
         <v>83.2</v>
       </c>
       <c r="AG158" t="n">
-        <v>985.8</v>
+        <v>0.9858</v>
       </c>
       <c r="AH158" t="n">
         <v>798.307</v>
@@ -31272,7 +31298,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="Y159" t="n">
-        <v>960.5</v>
+        <v>0.9605</v>
       </c>
       <c r="Z159" t="n">
         <v>812.607</v>
@@ -31296,7 +31322,7 @@
         <v>82.8</v>
       </c>
       <c r="AG159" t="n">
-        <v>980.8</v>
+        <v>0.9808</v>
       </c>
       <c r="AH159" t="n">
         <v>798.309</v>
@@ -31466,7 +31492,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="Y160" t="n">
-        <v>955.1</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="Z160" t="n">
         <v>812.6079999999999</v>
@@ -31490,7 +31516,7 @@
         <v>83</v>
       </c>
       <c r="AG160" t="n">
-        <v>982.7</v>
+        <v>0.9827</v>
       </c>
       <c r="AH160" t="n">
         <v>798.3099999999999</v>
@@ -31660,7 +31686,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="Y161" t="n">
-        <v>961.1</v>
+        <v>0.9611</v>
       </c>
       <c r="Z161" t="n">
         <v>812.61</v>
@@ -31684,7 +31710,7 @@
         <v>83.40000000000001</v>
       </c>
       <c r="AG161" t="n">
-        <v>987.8</v>
+        <v>0.9878</v>
       </c>
       <c r="AH161" t="n">
         <v>798.311</v>
@@ -31854,7 +31880,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="Y162" t="n">
-        <v>964.5</v>
+        <v>0.9645</v>
       </c>
       <c r="Z162" t="n">
         <v>812.611</v>
@@ -31878,7 +31904,7 @@
         <v>82.7</v>
       </c>
       <c r="AG162" t="n">
-        <v>979.3</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="AH162" t="n">
         <v>798.313</v>
@@ -32048,7 +32074,7 @@
         <v>81.5</v>
       </c>
       <c r="Y163" t="n">
-        <v>965.3</v>
+        <v>0.9653</v>
       </c>
       <c r="Z163" t="n">
         <v>812.612</v>
@@ -32072,7 +32098,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="AG163" t="n">
-        <v>972</v>
+        <v>0.972</v>
       </c>
       <c r="AH163" t="n">
         <v>798.314</v>
@@ -32242,7 +32268,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="Y164" t="n">
-        <v>961</v>
+        <v>0.961</v>
       </c>
       <c r="Z164" t="n">
         <v>812.614</v>
@@ -32266,7 +32292,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG164" t="n">
-        <v>966.4</v>
+        <v>0.9664</v>
       </c>
       <c r="AH164" t="n">
         <v>798.3150000000001</v>
@@ -32436,7 +32462,7 @@
         <v>81</v>
       </c>
       <c r="Y165" t="n">
-        <v>959.8</v>
+        <v>0.9598</v>
       </c>
       <c r="Z165" t="n">
         <v>812.615</v>
@@ -32460,7 +32486,7 @@
         <v>81.7</v>
       </c>
       <c r="AG165" t="n">
-        <v>967.4</v>
+        <v>0.9674</v>
       </c>
       <c r="AH165" t="n">
         <v>798.317</v>
@@ -32630,7 +32656,7 @@
         <v>81.3</v>
       </c>
       <c r="Y166" t="n">
-        <v>962.5</v>
+        <v>0.9625</v>
       </c>
       <c r="Z166" t="n">
         <v>812.616</v>
@@ -32654,7 +32680,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="AG166" t="n">
-        <v>960.5</v>
+        <v>0.9605</v>
       </c>
       <c r="AH166" t="n">
         <v>798.318</v>
@@ -32824,7 +32850,7 @@
         <v>81.3</v>
       </c>
       <c r="Y167" t="n">
-        <v>962.4</v>
+        <v>0.9624</v>
       </c>
       <c r="Z167" t="n">
         <v>812.6180000000001</v>
@@ -32848,7 +32874,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="AG167" t="n">
-        <v>957.9</v>
+        <v>0.9579</v>
       </c>
       <c r="AH167" t="n">
         <v>798.319</v>
@@ -33018,7 +33044,7 @@
         <v>80.7</v>
       </c>
       <c r="Y168" t="n">
-        <v>956.2</v>
+        <v>0.9562</v>
       </c>
       <c r="Z168" t="n">
         <v>812.619</v>
@@ -33042,7 +33068,7 @@
         <v>81.2</v>
       </c>
       <c r="AG168" t="n">
-        <v>961.8</v>
+        <v>0.9618</v>
       </c>
       <c r="AH168" t="n">
         <v>798.321</v>
@@ -33212,7 +33238,7 @@
         <v>80.5</v>
       </c>
       <c r="Y169" t="n">
-        <v>952.9</v>
+        <v>0.9529</v>
       </c>
       <c r="Z169" t="n">
         <v>812.62</v>
@@ -33236,7 +33262,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="AG169" t="n">
-        <v>963.5</v>
+        <v>0.9635</v>
       </c>
       <c r="AH169" t="n">
         <v>798.322</v>
@@ -33406,7 +33432,7 @@
         <v>80.09999999999999</v>
       </c>
       <c r="Y170" t="n">
-        <v>948.4</v>
+        <v>0.9484</v>
       </c>
       <c r="Z170" t="n">
         <v>812.622</v>
@@ -33430,7 +33456,7 @@
         <v>81.5</v>
       </c>
       <c r="AG170" t="n">
-        <v>965.7</v>
+        <v>0.9657</v>
       </c>
       <c r="AH170" t="n">
         <v>798.323</v>
@@ -33600,7 +33626,7 @@
         <v>80.5</v>
       </c>
       <c r="Y171" t="n">
-        <v>952.9</v>
+        <v>0.9529</v>
       </c>
       <c r="Z171" t="n">
         <v>812.623</v>
@@ -33624,7 +33650,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="AG171" t="n">
-        <v>972.4</v>
+        <v>0.9724</v>
       </c>
       <c r="AH171" t="n">
         <v>798.325</v>
@@ -33794,7 +33820,7 @@
         <v>80.3</v>
       </c>
       <c r="Y172" t="n">
-        <v>950.6</v>
+        <v>0.9506</v>
       </c>
       <c r="Z172" t="n">
         <v>812.624</v>
@@ -33818,7 +33844,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG172" t="n">
-        <v>969.9</v>
+        <v>0.9699</v>
       </c>
       <c r="AH172" t="n">
         <v>798.326</v>
@@ -33988,7 +34014,7 @@
         <v>80.7</v>
       </c>
       <c r="Y173" t="n">
-        <v>955.3</v>
+        <v>0.9553</v>
       </c>
       <c r="Z173" t="n">
         <v>812.626</v>
@@ -34012,7 +34038,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG173" t="n">
-        <v>966.9</v>
+        <v>0.9669</v>
       </c>
       <c r="AH173" t="n">
         <v>798.328</v>
@@ -34182,7 +34208,7 @@
         <v>80.40000000000001</v>
       </c>
       <c r="Y174" t="n">
-        <v>952.8</v>
+        <v>0.9528</v>
       </c>
       <c r="Z174" t="n">
         <v>812.627</v>
@@ -34206,7 +34232,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="AG174" t="n">
-        <v>972.4</v>
+        <v>0.9724</v>
       </c>
       <c r="AH174" t="n">
         <v>798.329</v>
@@ -34376,7 +34402,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="Y175" t="n">
-        <v>958.1</v>
+        <v>0.9581</v>
       </c>
       <c r="Z175" t="n">
         <v>812.628</v>
@@ -34400,7 +34426,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG175" t="n">
-        <v>967</v>
+        <v>0.967</v>
       </c>
       <c r="AH175" t="n">
         <v>798.33</v>
@@ -34570,7 +34596,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="Y176" t="n">
-        <v>964.3</v>
+        <v>0.9643</v>
       </c>
       <c r="Z176" t="n">
         <v>812.63</v>
@@ -34594,7 +34620,7 @@
         <v>81.3</v>
       </c>
       <c r="AG176" t="n">
-        <v>963.5</v>
+        <v>0.9635</v>
       </c>
       <c r="AH176" t="n">
         <v>798.332</v>
@@ -34764,7 +34790,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="Y177" t="n">
-        <v>966.1</v>
+        <v>0.9661</v>
       </c>
       <c r="Z177" t="n">
         <v>812.631</v>
@@ -34788,7 +34814,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="AG177" t="n">
-        <v>960.2</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="AH177" t="n">
         <v>798.333</v>
@@ -34958,7 +34984,7 @@
         <v>82.2</v>
       </c>
       <c r="Y178" t="n">
-        <v>973</v>
+        <v>0.973</v>
       </c>
       <c r="Z178" t="n">
         <v>812.6319999999999</v>
@@ -34982,7 +35008,7 @@
         <v>80.5</v>
       </c>
       <c r="AG178" t="n">
-        <v>953.6</v>
+        <v>0.9536</v>
       </c>
       <c r="AH178" t="n">
         <v>798.3339999999999</v>
@@ -35152,7 +35178,7 @@
         <v>82.2</v>
       </c>
       <c r="Y179" t="n">
-        <v>973.7</v>
+        <v>0.9737</v>
       </c>
       <c r="Z179" t="n">
         <v>812.634</v>
@@ -35176,7 +35202,7 @@
         <v>80</v>
       </c>
       <c r="AG179" t="n">
-        <v>948</v>
+        <v>0.948</v>
       </c>
       <c r="AH179" t="n">
         <v>798.336</v>
@@ -35346,7 +35372,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="Y180" t="n">
-        <v>976.4</v>
+        <v>0.9764</v>
       </c>
       <c r="Z180" t="n">
         <v>812.635</v>
@@ -35370,7 +35396,7 @@
         <v>79.8</v>
       </c>
       <c r="AG180" t="n">
-        <v>944.8</v>
+        <v>0.9448</v>
       </c>
       <c r="AH180" t="n">
         <v>798.337</v>
@@ -35540,7 +35566,7 @@
         <v>81.8</v>
       </c>
       <c r="Y181" t="n">
-        <v>969</v>
+        <v>0.969</v>
       </c>
       <c r="Z181" t="n">
         <v>812.636</v>
@@ -35564,7 +35590,7 @@
         <v>80.40000000000001</v>
       </c>
       <c r="AG181" t="n">
-        <v>951.8</v>
+        <v>0.9518</v>
       </c>
       <c r="AH181" t="n">
         <v>798.338</v>
@@ -35734,7 +35760,7 @@
         <v>81.8</v>
       </c>
       <c r="Y182" t="n">
-        <v>968.5</v>
+        <v>0.9685</v>
       </c>
       <c r="Z182" t="n">
         <v>812.638</v>
@@ -35758,7 +35784,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="AG182" t="n">
-        <v>954</v>
+        <v>0.954</v>
       </c>
       <c r="AH182" t="n">
         <v>798.3390000000001</v>
@@ -35928,7 +35954,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="Y183" t="n">
-        <v>973</v>
+        <v>0.973</v>
       </c>
       <c r="Z183" t="n">
         <v>812.639</v>
@@ -35952,7 +35978,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="AG183" t="n">
-        <v>961</v>
+        <v>0.961</v>
       </c>
       <c r="AH183" t="n">
         <v>798.341</v>
@@ -36122,7 +36148,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="Y184" t="n">
-        <v>970.3</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="Z184" t="n">
         <v>812.64</v>
@@ -36146,7 +36172,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG184" t="n">
-        <v>966.7</v>
+        <v>0.9667</v>
       </c>
       <c r="AH184" t="n">
         <v>798.342</v>
@@ -36316,7 +36342,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="Y185" t="n">
-        <v>971.9</v>
+        <v>0.9719</v>
       </c>
       <c r="Z185" t="n">
         <v>812.6420000000001</v>
@@ -36340,7 +36366,7 @@
         <v>81.7</v>
       </c>
       <c r="AG185" t="n">
-        <v>967.5</v>
+        <v>0.9675</v>
       </c>
       <c r="AH185" t="n">
         <v>798.343</v>
@@ -36510,7 +36536,7 @@
         <v>81.8</v>
       </c>
       <c r="Y186" t="n">
-        <v>968.4</v>
+        <v>0.9684</v>
       </c>
       <c r="Z186" t="n">
         <v>812.643</v>
@@ -36534,7 +36560,7 @@
         <v>81.8</v>
       </c>
       <c r="AG186" t="n">
-        <v>969.1</v>
+        <v>0.9691</v>
       </c>
       <c r="AH186" t="n">
         <v>798.345</v>
@@ -36704,7 +36730,7 @@
         <v>81.8</v>
       </c>
       <c r="Y187" t="n">
-        <v>969.2</v>
+        <v>0.9692</v>
       </c>
       <c r="Z187" t="n">
         <v>812.644</v>
@@ -36728,7 +36754,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="AG187" t="n">
-        <v>963.7</v>
+        <v>0.9637</v>
       </c>
       <c r="AH187" t="n">
         <v>798.346</v>
@@ -36898,7 +36924,7 @@
         <v>81.3</v>
       </c>
       <c r="Y188" t="n">
-        <v>963</v>
+        <v>0.963</v>
       </c>
       <c r="Z188" t="n">
         <v>812.646</v>
@@ -36922,7 +36948,7 @@
         <v>81.7</v>
       </c>
       <c r="AG188" t="n">
-        <v>967.8</v>
+        <v>0.9678</v>
       </c>
       <c r="AH188" t="n">
         <v>798.348</v>
@@ -37092,7 +37118,7 @@
         <v>80.8</v>
       </c>
       <c r="Y189" t="n">
-        <v>957.6</v>
+        <v>0.9576</v>
       </c>
       <c r="Z189" t="n">
         <v>812.647</v>
@@ -37116,7 +37142,7 @@
         <v>81.5</v>
       </c>
       <c r="AG189" t="n">
-        <v>965</v>
+        <v>0.965</v>
       </c>
       <c r="AH189" t="n">
         <v>798.349</v>
@@ -37286,7 +37312,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="Y190" t="n">
-        <v>954.1</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="Z190" t="n">
         <v>812.648</v>
@@ -37310,7 +37336,7 @@
         <v>81</v>
       </c>
       <c r="AG190" t="n">
-        <v>959.4</v>
+        <v>0.9594</v>
       </c>
       <c r="AH190" t="n">
         <v>798.35</v>
@@ -37480,7 +37506,7 @@
         <v>80.7</v>
       </c>
       <c r="Y191" t="n">
-        <v>955.4</v>
+        <v>0.9554</v>
       </c>
       <c r="Z191" t="n">
         <v>812.65</v>
@@ -37504,7 +37530,7 @@
         <v>80.7</v>
       </c>
       <c r="AG191" t="n">
-        <v>956.1</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="AH191" t="n">
         <v>798.352</v>
@@ -37674,7 +37700,7 @@
         <v>80.8</v>
       </c>
       <c r="Y192" t="n">
-        <v>956.5</v>
+        <v>0.9565</v>
       </c>
       <c r="Z192" t="n">
         <v>812.651</v>
@@ -37698,7 +37724,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="AG192" t="n">
-        <v>960</v>
+        <v>0.96</v>
       </c>
       <c r="AH192" t="n">
         <v>798.353</v>
@@ -37868,7 +37894,7 @@
         <v>80.3</v>
       </c>
       <c r="Y193" t="n">
-        <v>951.2</v>
+        <v>0.9512</v>
       </c>
       <c r="Z193" t="n">
         <v>812.652</v>
@@ -37892,7 +37918,7 @@
         <v>81.5</v>
       </c>
       <c r="AG193" t="n">
-        <v>965.3</v>
+        <v>0.9653</v>
       </c>
       <c r="AH193" t="n">
         <v>798.354</v>
@@ -38062,7 +38088,7 @@
         <v>80.40000000000001</v>
       </c>
       <c r="Y194" t="n">
-        <v>952.3</v>
+        <v>0.9523</v>
       </c>
       <c r="Z194" t="n">
         <v>812.654</v>
@@ -38086,7 +38112,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG194" t="n">
-        <v>966.1</v>
+        <v>0.9661</v>
       </c>
       <c r="AH194" t="n">
         <v>798.356</v>
@@ -38256,7 +38282,7 @@
         <v>80</v>
       </c>
       <c r="Y195" t="n">
-        <v>947.8</v>
+        <v>0.9478</v>
       </c>
       <c r="Z195" t="n">
         <v>812.655</v>
@@ -38280,7 +38306,7 @@
         <v>81.7</v>
       </c>
       <c r="AG195" t="n">
-        <v>967.5</v>
+        <v>0.9675</v>
       </c>
       <c r="AH195" t="n">
         <v>798.357</v>
@@ -38450,7 +38476,7 @@
         <v>80.5</v>
       </c>
       <c r="Y196" t="n">
-        <v>953.1</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="Z196" t="n">
         <v>812.6559999999999</v>
@@ -38474,7 +38500,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG196" t="n">
-        <v>967</v>
+        <v>0.967</v>
       </c>
       <c r="AH196" t="n">
         <v>798.3579999999999</v>
@@ -38644,7 +38670,7 @@
         <v>80.3</v>
       </c>
       <c r="Y197" t="n">
-        <v>951.2</v>
+        <v>0.9512</v>
       </c>
       <c r="Z197" t="n">
         <v>812.658</v>
@@ -38668,7 +38694,7 @@
         <v>81.8</v>
       </c>
       <c r="AG197" t="n">
-        <v>969.4</v>
+        <v>0.9694</v>
       </c>
       <c r="AH197" t="n">
         <v>798.36</v>
@@ -38838,7 +38864,7 @@
         <v>80.3</v>
       </c>
       <c r="Y198" t="n">
-        <v>950.7</v>
+        <v>0.9507</v>
       </c>
       <c r="Z198" t="n">
         <v>812.659</v>
@@ -38862,7 +38888,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="AG198" t="n">
-        <v>963.7</v>
+        <v>0.9637</v>
       </c>
       <c r="AH198" t="n">
         <v>798.361</v>
@@ -39032,7 +39058,7 @@
         <v>80</v>
       </c>
       <c r="Y199" t="n">
-        <v>947.1</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="Z199" t="n">
         <v>812.66</v>
@@ -39056,7 +39082,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="AG199" t="n">
-        <v>958.2</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="AH199" t="n">
         <v>798.362</v>
@@ -39226,7 +39252,7 @@
         <v>79.7</v>
       </c>
       <c r="Y200" t="n">
-        <v>943.5</v>
+        <v>0.9435</v>
       </c>
       <c r="Z200" t="n">
         <v>812.662</v>
@@ -39250,7 +39276,7 @@
         <v>81</v>
       </c>
       <c r="AG200" t="n">
-        <v>959.9</v>
+        <v>0.9599</v>
       </c>
       <c r="AH200" t="n">
         <v>798.364</v>
@@ -39420,7 +39446,7 @@
         <v>80.2</v>
       </c>
       <c r="Y201" t="n">
-        <v>950.4</v>
+        <v>0.9504</v>
       </c>
       <c r="Z201" t="n">
         <v>812.663</v>
@@ -39444,7 +39470,7 @@
         <v>80.8</v>
       </c>
       <c r="AG201" t="n">
-        <v>957.3</v>
+        <v>0.9573</v>
       </c>
       <c r="AH201" t="n">
         <v>798.365</v>
@@ -39614,7 +39640,7 @@
         <v>80.3</v>
       </c>
       <c r="Y202" t="n">
-        <v>950.6</v>
+        <v>0.9506</v>
       </c>
       <c r="Z202" t="n">
         <v>812.664</v>
@@ -39638,7 +39664,7 @@
         <v>80.5</v>
       </c>
       <c r="AG202" t="n">
-        <v>953.2</v>
+        <v>0.9532</v>
       </c>
       <c r="AH202" t="n">
         <v>798.366</v>
@@ -39808,7 +39834,7 @@
         <v>79.90000000000001</v>
       </c>
       <c r="Y203" t="n">
-        <v>946.5</v>
+        <v>0.9465</v>
       </c>
       <c r="Z203" t="n">
         <v>812.6660000000001</v>
@@ -39832,7 +39858,7 @@
         <v>80.2</v>
       </c>
       <c r="AG203" t="n">
-        <v>950.2</v>
+        <v>0.9502</v>
       </c>
       <c r="AH203" t="n">
         <v>798.3680000000001</v>
@@ -40002,7 +40028,7 @@
         <v>80.40000000000001</v>
       </c>
       <c r="Y204" t="n">
-        <v>952.6</v>
+        <v>0.9526</v>
       </c>
       <c r="Z204" t="n">
         <v>812.667</v>
@@ -40026,7 +40052,7 @@
         <v>81</v>
       </c>
       <c r="AG204" t="n">
-        <v>958.9</v>
+        <v>0.9589</v>
       </c>
       <c r="AH204" t="n">
         <v>798.369</v>
@@ -40196,7 +40222,7 @@
         <v>80.40000000000001</v>
       </c>
       <c r="Y205" t="n">
-        <v>952.8</v>
+        <v>0.9528</v>
       </c>
       <c r="Z205" t="n">
         <v>812.668</v>
@@ -40220,7 +40246,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="AG205" t="n">
-        <v>961.1</v>
+        <v>0.9611</v>
       </c>
       <c r="AH205" t="n">
         <v>798.37</v>
@@ -40390,7 +40416,7 @@
         <v>80.5</v>
       </c>
       <c r="Y206" t="n">
-        <v>953.5</v>
+        <v>0.9535</v>
       </c>
       <c r="Z206" t="n">
         <v>812.67</v>
@@ -40414,7 +40440,7 @@
         <v>81.8</v>
       </c>
       <c r="AG206" t="n">
-        <v>968.5</v>
+        <v>0.9685</v>
       </c>
       <c r="AH206" t="n">
         <v>798.372</v>
@@ -40584,7 +40610,7 @@
         <v>81.2</v>
       </c>
       <c r="Y207" t="n">
-        <v>961.9</v>
+        <v>0.9619</v>
       </c>
       <c r="Z207" t="n">
         <v>812.671</v>
@@ -40608,7 +40634,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG207" t="n">
-        <v>970.5</v>
+        <v>0.9705</v>
       </c>
       <c r="AH207" t="n">
         <v>798.373</v>
@@ -40778,7 +40804,7 @@
         <v>81.5</v>
       </c>
       <c r="Y208" t="n">
-        <v>965.3</v>
+        <v>0.9653</v>
       </c>
       <c r="Z208" t="n">
         <v>812.672</v>
@@ -40802,7 +40828,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="AG208" t="n">
-        <v>972.7</v>
+        <v>0.9727</v>
       </c>
       <c r="AH208" t="n">
         <v>798.374</v>
@@ -40972,7 +40998,7 @@
         <v>81.3</v>
       </c>
       <c r="Y209" t="n">
-        <v>963.4</v>
+        <v>0.9634</v>
       </c>
       <c r="Z209" t="n">
         <v>812.674</v>
@@ -40996,7 +41022,7 @@
         <v>82.3</v>
       </c>
       <c r="AG209" t="n">
-        <v>974.5</v>
+        <v>0.9745</v>
       </c>
       <c r="AH209" t="n">
         <v>798.376</v>
@@ -41166,7 +41192,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="Y210" t="n">
-        <v>966.9</v>
+        <v>0.9669</v>
       </c>
       <c r="Z210" t="n">
         <v>812.675</v>
@@ -41190,7 +41216,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="AG210" t="n">
-        <v>972.3</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="AH210" t="n">
         <v>798.377</v>
@@ -41360,7 +41386,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="Y211" t="n">
-        <v>963.8</v>
+        <v>0.9638</v>
       </c>
       <c r="Z211" t="n">
         <v>812.676</v>
@@ -41384,7 +41410,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG211" t="n">
-        <v>969.9</v>
+        <v>0.9699</v>
       </c>
       <c r="AH211" t="n">
         <v>798.378</v>
@@ -41554,7 +41580,7 @@
         <v>81.3</v>
       </c>
       <c r="Y212" t="n">
-        <v>962.4</v>
+        <v>0.9624</v>
       </c>
       <c r="Z212" t="n">
         <v>812.678</v>
@@ -41578,7 +41604,7 @@
         <v>81.7</v>
       </c>
       <c r="AG212" t="n">
-        <v>967.7</v>
+        <v>0.9677</v>
       </c>
       <c r="AH212" t="n">
         <v>798.38</v>
@@ -41748,7 +41774,7 @@
         <v>81.2</v>
       </c>
       <c r="Y213" t="n">
-        <v>961.6</v>
+        <v>0.9616</v>
       </c>
       <c r="Z213" t="n">
         <v>812.679</v>
@@ -41772,7 +41798,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG213" t="n">
-        <v>966.5</v>
+        <v>0.9665</v>
       </c>
       <c r="AH213" t="n">
         <v>798.381</v>
@@ -41942,7 +41968,7 @@
         <v>80.7</v>
       </c>
       <c r="Y214" t="n">
-        <v>955.9</v>
+        <v>0.9559</v>
       </c>
       <c r="Z214" t="n">
         <v>812.6799999999999</v>
@@ -41966,7 +41992,7 @@
         <v>81.8</v>
       </c>
       <c r="AG214" t="n">
-        <v>968.7</v>
+        <v>0.9687</v>
       </c>
       <c r="AH214" t="n">
         <v>798.3819999999999</v>
@@ -42136,7 +42162,7 @@
         <v>80.8</v>
       </c>
       <c r="Y215" t="n">
-        <v>956.7</v>
+        <v>0.9567</v>
       </c>
       <c r="Z215" t="n">
         <v>812.682</v>
@@ -42160,7 +42186,7 @@
         <v>81.8</v>
       </c>
       <c r="AG215" t="n">
-        <v>969</v>
+        <v>0.969</v>
       </c>
       <c r="AH215" t="n">
         <v>798.384</v>
@@ -42330,7 +42356,7 @@
         <v>81.3</v>
       </c>
       <c r="Y216" t="n">
-        <v>962.4</v>
+        <v>0.9624</v>
       </c>
       <c r="Z216" t="n">
         <v>812.683</v>
@@ -42354,7 +42380,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="AG216" t="n">
-        <v>972.6</v>
+        <v>0.9726</v>
       </c>
       <c r="AH216" t="n">
         <v>798.385</v>
@@ -42524,7 +42550,7 @@
         <v>81.7</v>
       </c>
       <c r="Y217" t="n">
-        <v>968.1</v>
+        <v>0.9681</v>
       </c>
       <c r="Z217" t="n">
         <v>812.684</v>
@@ -42548,7 +42574,7 @@
         <v>81.8</v>
       </c>
       <c r="AG217" t="n">
-        <v>968.5</v>
+        <v>0.9685</v>
       </c>
       <c r="AH217" t="n">
         <v>798.386</v>
@@ -42718,7 +42744,7 @@
         <v>81.5</v>
       </c>
       <c r="Y218" t="n">
-        <v>965.2</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="Z218" t="n">
         <v>812.686</v>
@@ -42742,7 +42768,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="AG218" t="n">
-        <v>972.6</v>
+        <v>0.9726</v>
       </c>
       <c r="AH218" t="n">
         <v>798.388</v>
@@ -42912,7 +42938,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="Y219" t="n">
-        <v>964.3</v>
+        <v>0.9643</v>
       </c>
       <c r="Z219" t="n">
         <v>812.687</v>
@@ -42936,7 +42962,7 @@
         <v>82</v>
       </c>
       <c r="AG219" t="n">
-        <v>970.7</v>
+        <v>0.9707</v>
       </c>
       <c r="AH219" t="n">
         <v>798.389</v>
@@ -43106,7 +43132,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="Y220" t="n">
-        <v>966.6</v>
+        <v>0.9666</v>
       </c>
       <c r="Z220" t="n">
         <v>812.688</v>
@@ -43130,7 +43156,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="AG220" t="n">
-        <v>972.3</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="AH220" t="n">
         <v>798.39</v>
@@ -43300,7 +43326,7 @@
         <v>81.3</v>
       </c>
       <c r="Y221" t="n">
-        <v>963.3</v>
+        <v>0.9633</v>
       </c>
       <c r="Z221" t="n">
         <v>812.6900000000001</v>
@@ -43324,7 +43350,7 @@
         <v>81.5</v>
       </c>
       <c r="AG221" t="n">
-        <v>965.5</v>
+        <v>0.9655</v>
       </c>
       <c r="AH221" t="n">
         <v>798.3920000000001</v>
@@ -43494,7 +43520,7 @@
         <v>81.7</v>
       </c>
       <c r="Y222" t="n">
-        <v>968</v>
+        <v>0.968</v>
       </c>
       <c r="Z222" t="n">
         <v>812.691</v>
@@ -43518,7 +43544,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="AG222" t="n">
-        <v>964.5</v>
+        <v>0.9645</v>
       </c>
       <c r="AH222" t="n">
         <v>798.393</v>
@@ -43688,7 +43714,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="Y223" t="n">
-        <v>970.6</v>
+        <v>0.9706</v>
       </c>
       <c r="Z223" t="n">
         <v>812.692</v>
@@ -43712,7 +43738,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG223" t="n">
-        <v>969.7</v>
+        <v>0.9697</v>
       </c>
       <c r="AH223" t="n">
         <v>798.394</v>
@@ -43882,7 +43908,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="Y224" t="n">
-        <v>964.3</v>
+        <v>0.9643</v>
       </c>
       <c r="Z224" t="n">
         <v>812.694</v>
@@ -43906,7 +43932,7 @@
         <v>82.3</v>
       </c>
       <c r="AG224" t="n">
-        <v>975.4</v>
+        <v>0.9754</v>
       </c>
       <c r="AH224" t="n">
         <v>798.396</v>
@@ -44076,7 +44102,7 @@
         <v>81.2</v>
       </c>
       <c r="Y225" t="n">
-        <v>961.8</v>
+        <v>0.9618</v>
       </c>
       <c r="Z225" t="n">
         <v>812.6950000000001</v>
@@ -44100,7 +44126,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="AG225" t="n">
-        <v>971.9</v>
+        <v>0.9719</v>
       </c>
       <c r="AH225" t="n">
         <v>798.397</v>
@@ -44270,7 +44296,7 @@
         <v>81.5</v>
       </c>
       <c r="Y226" t="n">
-        <v>965.1</v>
+        <v>0.9651</v>
       </c>
       <c r="Z226" t="n">
         <v>812.696</v>
@@ -44294,7 +44320,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="AG226" t="n">
-        <v>972</v>
+        <v>0.972</v>
       </c>
       <c r="AH226" t="n">
         <v>798.399</v>
@@ -44464,7 +44490,7 @@
         <v>81</v>
       </c>
       <c r="Y227" t="n">
-        <v>959.6</v>
+        <v>0.9596</v>
       </c>
       <c r="Z227" t="n">
         <v>812.698</v>
@@ -44488,7 +44514,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG227" t="n">
-        <v>970.3</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="AH227" t="n">
         <v>798.4</v>
@@ -44658,7 +44684,7 @@
         <v>80.7</v>
       </c>
       <c r="Y228" t="n">
-        <v>956</v>
+        <v>0.956</v>
       </c>
       <c r="Z228" t="n">
         <v>812.699</v>
@@ -44682,7 +44708,7 @@
         <v>82.3</v>
       </c>
       <c r="AG228" t="n">
-        <v>974.9</v>
+        <v>0.9749</v>
       </c>
       <c r="AH228" t="n">
         <v>798.401</v>
@@ -44852,7 +44878,7 @@
         <v>80.3</v>
       </c>
       <c r="Y229" t="n">
-        <v>950.9</v>
+        <v>0.9509</v>
       </c>
       <c r="Z229" t="n">
         <v>812.7</v>
@@ -44876,7 +44902,7 @@
         <v>81.8</v>
       </c>
       <c r="AG229" t="n">
-        <v>968.4</v>
+        <v>0.9684</v>
       </c>
       <c r="AH229" t="n">
         <v>798.403</v>
@@ -45046,7 +45072,7 @@
         <v>81</v>
       </c>
       <c r="Y230" t="n">
-        <v>959.6</v>
+        <v>0.9596</v>
       </c>
       <c r="Z230" t="n">
         <v>812.702</v>
@@ -45070,7 +45096,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG230" t="n">
-        <v>966.7</v>
+        <v>0.9667</v>
       </c>
       <c r="AH230" t="n">
         <v>798.404</v>
@@ -45240,7 +45266,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="Y231" t="n">
-        <v>964.2</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="Z231" t="n">
         <v>812.703</v>
@@ -45264,7 +45290,7 @@
         <v>81.7</v>
       </c>
       <c r="AG231" t="n">
-        <v>967.2</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="AH231" t="n">
         <v>798.405</v>
@@ -45434,7 +45460,7 @@
         <v>81.5</v>
       </c>
       <c r="Y232" t="n">
-        <v>965.7</v>
+        <v>0.9657</v>
       </c>
       <c r="Z232" t="n">
         <v>812.704</v>
@@ -45458,7 +45484,7 @@
         <v>81.7</v>
       </c>
       <c r="AG232" t="n">
-        <v>968.1</v>
+        <v>0.9681</v>
       </c>
       <c r="AH232" t="n">
         <v>798.407</v>
@@ -45628,7 +45654,7 @@
         <v>82</v>
       </c>
       <c r="Y233" t="n">
-        <v>971.4</v>
+        <v>0.9714</v>
       </c>
       <c r="Z233" t="n">
         <v>812.706</v>
@@ -45652,7 +45678,7 @@
         <v>82</v>
       </c>
       <c r="AG233" t="n">
-        <v>971.4</v>
+        <v>0.9714</v>
       </c>
       <c r="AH233" t="n">
         <v>798.408</v>
@@ -45822,7 +45848,7 @@
         <v>82.3</v>
       </c>
       <c r="Y234" t="n">
-        <v>974.3</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="Z234" t="n">
         <v>812.707</v>
@@ -45846,7 +45872,7 @@
         <v>82.3</v>
       </c>
       <c r="AG234" t="n">
-        <v>975.3</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="AH234" t="n">
         <v>798.409</v>
@@ -46016,7 +46042,7 @@
         <v>82</v>
       </c>
       <c r="Y235" t="n">
-        <v>971</v>
+        <v>0.971</v>
       </c>
       <c r="Z235" t="n">
         <v>812.708</v>
@@ -46040,7 +46066,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG235" t="n">
-        <v>970.4</v>
+        <v>0.9704</v>
       </c>
       <c r="AH235" t="n">
         <v>798.4109999999999</v>
@@ -46210,7 +46236,7 @@
         <v>81.8</v>
       </c>
       <c r="Y236" t="n">
-        <v>969.2</v>
+        <v>0.9692</v>
       </c>
       <c r="Z236" t="n">
         <v>812.71</v>
@@ -46234,7 +46260,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="AG236" t="n">
-        <v>964.3</v>
+        <v>0.9643</v>
       </c>
       <c r="AH236" t="n">
         <v>798.412</v>
@@ -46404,7 +46430,7 @@
         <v>82.3</v>
       </c>
       <c r="Y237" t="n">
-        <v>975.3</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="Z237" t="n">
         <v>812.711</v>
@@ -46428,7 +46454,7 @@
         <v>81.7</v>
       </c>
       <c r="AG237" t="n">
-        <v>967.5</v>
+        <v>0.9675</v>
       </c>
       <c r="AH237" t="n">
         <v>798.413</v>
@@ -46598,7 +46624,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="Y238" t="n">
-        <v>976.1</v>
+        <v>0.9761</v>
       </c>
       <c r="Z238" t="n">
         <v>812.712</v>
@@ -46622,7 +46648,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG238" t="n">
-        <v>966.6</v>
+        <v>0.9666</v>
       </c>
       <c r="AH238" t="n">
         <v>798.415</v>
@@ -46792,7 +46818,7 @@
         <v>82.2</v>
       </c>
       <c r="Y239" t="n">
-        <v>973.5</v>
+        <v>0.9735</v>
       </c>
       <c r="Z239" t="n">
         <v>812.7140000000001</v>
@@ -46816,7 +46842,7 @@
         <v>81.3</v>
       </c>
       <c r="AG239" t="n">
-        <v>962.6</v>
+        <v>0.9626</v>
       </c>
       <c r="AH239" t="n">
         <v>798.4160000000001</v>
@@ -46986,7 +47012,7 @@
         <v>82.3</v>
       </c>
       <c r="Y240" t="n">
-        <v>975.3</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="Z240" t="n">
         <v>812.715</v>
@@ -47010,7 +47036,7 @@
         <v>80.8</v>
       </c>
       <c r="AG240" t="n">
-        <v>956.6</v>
+        <v>0.9566</v>
       </c>
       <c r="AH240" t="n">
         <v>798.417</v>
@@ -47180,7 +47206,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="Y241" t="n">
-        <v>976.1</v>
+        <v>0.9761</v>
       </c>
       <c r="Z241" t="n">
         <v>812.716</v>
@@ -47204,7 +47230,7 @@
         <v>81</v>
       </c>
       <c r="AG241" t="n">
-        <v>959.2</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="AH241" t="n">
         <v>798.419</v>
@@ -47374,7 +47400,7 @@
         <v>82</v>
       </c>
       <c r="Y242" t="n">
-        <v>970.9</v>
+        <v>0.9709</v>
       </c>
       <c r="Z242" t="n">
         <v>812.718</v>
@@ -47398,7 +47424,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="AG242" t="n">
-        <v>958.6</v>
+        <v>0.9586</v>
       </c>
       <c r="AH242" t="n">
         <v>798.42</v>
@@ -47568,7 +47594,7 @@
         <v>82</v>
       </c>
       <c r="Y243" t="n">
-        <v>970.8</v>
+        <v>0.9708</v>
       </c>
       <c r="Z243" t="n">
         <v>812.7190000000001</v>
@@ -47592,7 +47618,7 @@
         <v>81.2</v>
       </c>
       <c r="AG243" t="n">
-        <v>961.2</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="AH243" t="n">
         <v>798.421</v>
@@ -47762,7 +47788,7 @@
         <v>82.3</v>
       </c>
       <c r="Y244" t="n">
-        <v>974.3</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="Z244" t="n">
         <v>812.721</v>
@@ -47786,7 +47812,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="AG244" t="n">
-        <v>957.9</v>
+        <v>0.9579</v>
       </c>
       <c r="AH244" t="n">
         <v>798.423</v>
@@ -47956,7 +47982,7 @@
         <v>82.5</v>
       </c>
       <c r="Y245" t="n">
-        <v>976.8</v>
+        <v>0.9768</v>
       </c>
       <c r="Z245" t="n">
         <v>812.722</v>
@@ -47980,7 +48006,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="AG245" t="n">
-        <v>954.8</v>
+        <v>0.9548</v>
       </c>
       <c r="AH245" t="n">
         <v>798.424</v>
@@ -48150,7 +48176,7 @@
         <v>82.7</v>
       </c>
       <c r="Y246" t="n">
-        <v>979.8</v>
+        <v>0.9798</v>
       </c>
       <c r="Z246" t="n">
         <v>812.723</v>
@@ -48174,7 +48200,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="AG246" t="n">
-        <v>958.5</v>
+        <v>0.9585</v>
       </c>
       <c r="AH246" t="n">
         <v>798.425</v>
@@ -48344,7 +48370,7 @@
         <v>82.7</v>
       </c>
       <c r="Y247" t="n">
-        <v>979</v>
+        <v>0.979</v>
       </c>
       <c r="Z247" t="n">
         <v>812.725</v>
@@ -48368,7 +48394,7 @@
         <v>80.7</v>
       </c>
       <c r="AG247" t="n">
-        <v>955.7</v>
+        <v>0.9557</v>
       </c>
       <c r="AH247" t="n">
         <v>798.427</v>
@@ -48538,7 +48564,7 @@
         <v>82.3</v>
       </c>
       <c r="Y248" t="n">
-        <v>974.3</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="Z248" t="n">
         <v>812.726</v>
@@ -48562,7 +48588,7 @@
         <v>80.7</v>
       </c>
       <c r="AG248" t="n">
-        <v>956.1</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="AH248" t="n">
         <v>798.428</v>
@@ -48732,7 +48758,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="Y249" t="n">
-        <v>973</v>
+        <v>0.973</v>
       </c>
       <c r="Z249" t="n">
         <v>812.727</v>
@@ -48756,7 +48782,7 @@
         <v>81</v>
       </c>
       <c r="AG249" t="n">
-        <v>959.1</v>
+        <v>0.9591</v>
       </c>
       <c r="AH249" t="n">
         <v>798.429</v>
@@ -48926,7 +48952,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="Y250" t="n">
-        <v>966.4</v>
+        <v>0.9664</v>
       </c>
       <c r="Z250" t="n">
         <v>812.729</v>
@@ -48950,7 +48976,7 @@
         <v>80.8</v>
       </c>
       <c r="AG250" t="n">
-        <v>956.6</v>
+        <v>0.9566</v>
       </c>
       <c r="AH250" t="n">
         <v>798.431</v>
@@ -49120,7 +49146,7 @@
         <v>81.7</v>
       </c>
       <c r="Y251" t="n">
-        <v>967.9</v>
+        <v>0.9679</v>
       </c>
       <c r="Z251" t="n">
         <v>812.73</v>
@@ -49144,7 +49170,7 @@
         <v>80.8</v>
       </c>
       <c r="AG251" t="n">
-        <v>956.4</v>
+        <v>0.9564</v>
       </c>
       <c r="AH251" t="n">
         <v>798.432</v>
@@ -49314,7 +49340,7 @@
         <v>81.5</v>
       </c>
       <c r="Y252" t="n">
-        <v>965.6</v>
+        <v>0.9656</v>
       </c>
       <c r="Z252" t="n">
         <v>812.731</v>
@@ -49338,7 +49364,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="AG252" t="n">
-        <v>955</v>
+        <v>0.955</v>
       </c>
       <c r="AH252" t="n">
         <v>798.433</v>
@@ -49508,7 +49534,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="Y253" t="n">
-        <v>960.3</v>
+        <v>0.9603</v>
       </c>
       <c r="Z253" t="n">
         <v>812.7329999999999</v>
@@ -49532,7 +49558,7 @@
         <v>80.7</v>
       </c>
       <c r="AG253" t="n">
-        <v>955.9</v>
+        <v>0.9559</v>
       </c>
       <c r="AH253" t="n">
         <v>798.4349999999999</v>
@@ -49702,7 +49728,7 @@
         <v>81</v>
       </c>
       <c r="Y254" t="n">
-        <v>959.9</v>
+        <v>0.9599</v>
       </c>
       <c r="Z254" t="n">
         <v>812.734</v>
@@ -49726,7 +49752,7 @@
         <v>80.8</v>
       </c>
       <c r="AG254" t="n">
-        <v>956.9</v>
+        <v>0.9569</v>
       </c>
       <c r="AH254" t="n">
         <v>798.436</v>
@@ -49896,7 +49922,7 @@
         <v>81.7</v>
       </c>
       <c r="Y255" t="n">
-        <v>967.3</v>
+        <v>0.9673</v>
       </c>
       <c r="Z255" t="n">
         <v>812.735</v>
@@ -49920,7 +49946,7 @@
         <v>80.40000000000001</v>
       </c>
       <c r="AG255" t="n">
-        <v>951.9</v>
+        <v>0.9519</v>
       </c>
       <c r="AH255" t="n">
         <v>798.437</v>
@@ -50090,7 +50116,7 @@
         <v>81.3</v>
       </c>
       <c r="Y256" t="n">
-        <v>963</v>
+        <v>0.963</v>
       </c>
       <c r="Z256" t="n">
         <v>812.737</v>
@@ -50114,7 +50140,7 @@
         <v>80.09999999999999</v>
       </c>
       <c r="AG256" t="n">
-        <v>948.6</v>
+        <v>0.9486</v>
       </c>
       <c r="AH256" t="n">
         <v>798.439</v>
@@ -50284,7 +50310,7 @@
         <v>81.8</v>
       </c>
       <c r="Y257" t="n">
-        <v>968.5</v>
+        <v>0.9685</v>
       </c>
       <c r="Z257" t="n">
         <v>812.7380000000001</v>
@@ -50308,7 +50334,7 @@
         <v>80.8</v>
       </c>
       <c r="AG257" t="n">
-        <v>957.4</v>
+        <v>0.9574</v>
       </c>
       <c r="AH257" t="n">
         <v>798.4400000000001</v>
@@ -50478,7 +50504,7 @@
         <v>81.3</v>
       </c>
       <c r="Y258" t="n">
-        <v>963</v>
+        <v>0.963</v>
       </c>
       <c r="Z258" t="n">
         <v>812.739</v>
@@ -50502,7 +50528,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="AG258" t="n">
-        <v>960.6</v>
+        <v>0.9606</v>
       </c>
       <c r="AH258" t="n">
         <v>798.441</v>
@@ -50672,7 +50698,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="Y259" t="n">
-        <v>964.7</v>
+        <v>0.9647</v>
       </c>
       <c r="Z259" t="n">
         <v>812.741</v>
@@ -50696,7 +50722,7 @@
         <v>81.7</v>
       </c>
       <c r="AG259" t="n">
-        <v>967.5</v>
+        <v>0.9675</v>
       </c>
       <c r="AH259" t="n">
         <v>798.443</v>
@@ -50866,7 +50892,7 @@
         <v>81</v>
       </c>
       <c r="Y260" t="n">
-        <v>959.2</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="Z260" t="n">
         <v>812.742</v>
@@ -50890,7 +50916,7 @@
         <v>81.8</v>
       </c>
       <c r="AG260" t="n">
-        <v>968.9</v>
+        <v>0.9689</v>
       </c>
       <c r="AH260" t="n">
         <v>798.444</v>
@@ -51060,7 +51086,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="Y261" t="n">
-        <v>960.3</v>
+        <v>0.9603</v>
       </c>
       <c r="Z261" t="n">
         <v>812.7430000000001</v>
@@ -51084,7 +51110,7 @@
         <v>81.3</v>
       </c>
       <c r="AG261" t="n">
-        <v>963.1</v>
+        <v>0.9631</v>
       </c>
       <c r="AH261" t="n">
         <v>798.4450000000001</v>
@@ -51254,7 +51280,7 @@
         <v>81.2</v>
       </c>
       <c r="Y262" t="n">
-        <v>961.3</v>
+        <v>0.9613</v>
       </c>
       <c r="Z262" t="n">
         <v>812.745</v>
@@ -51278,7 +51304,7 @@
         <v>81</v>
       </c>
       <c r="AG262" t="n">
-        <v>959</v>
+        <v>0.959</v>
       </c>
       <c r="AH262" t="n">
         <v>798.447</v>
@@ -51448,7 +51474,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="Y263" t="n">
-        <v>958.4</v>
+        <v>0.9584</v>
       </c>
       <c r="Z263" t="n">
         <v>812.746</v>
@@ -51472,7 +51498,7 @@
         <v>81.3</v>
       </c>
       <c r="AG263" t="n">
-        <v>963</v>
+        <v>0.963</v>
       </c>
       <c r="AH263" t="n">
         <v>798.448</v>
@@ -51642,7 +51668,7 @@
         <v>81.3</v>
       </c>
       <c r="Y264" t="n">
-        <v>962.7</v>
+        <v>0.9627</v>
       </c>
       <c r="Z264" t="n">
         <v>812.747</v>
@@ -51666,7 +51692,7 @@
         <v>81</v>
       </c>
       <c r="AG264" t="n">
-        <v>959.5</v>
+        <v>0.9595</v>
       </c>
       <c r="AH264" t="n">
         <v>798.449</v>
@@ -51836,7 +51862,7 @@
         <v>81.5</v>
       </c>
       <c r="Y265" t="n">
-        <v>965.4</v>
+        <v>0.9654</v>
       </c>
       <c r="Z265" t="n">
         <v>812.749</v>
@@ -51860,7 +51886,7 @@
         <v>81.5</v>
       </c>
       <c r="AG265" t="n">
-        <v>965.5</v>
+        <v>0.9655</v>
       </c>
       <c r="AH265" t="n">
         <v>798.451</v>
@@ -52030,7 +52056,7 @@
         <v>81.2</v>
       </c>
       <c r="Y266" t="n">
-        <v>961.3</v>
+        <v>0.9613</v>
       </c>
       <c r="Z266" t="n">
         <v>812.75</v>
@@ -52054,7 +52080,7 @@
         <v>81.2</v>
       </c>
       <c r="AG266" t="n">
-        <v>961.8</v>
+        <v>0.9618</v>
       </c>
       <c r="AH266" t="n">
         <v>798.452</v>
@@ -52224,7 +52250,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="Y267" t="n">
-        <v>957.8</v>
+        <v>0.9578</v>
       </c>
       <c r="Z267" t="n">
         <v>812.751</v>
@@ -52248,7 +52274,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG267" t="n">
-        <v>966.6</v>
+        <v>0.9666</v>
       </c>
       <c r="AH267" t="n">
         <v>798.453</v>
@@ -52418,7 +52444,7 @@
         <v>80.8</v>
       </c>
       <c r="Y268" t="n">
-        <v>956.7</v>
+        <v>0.9567</v>
       </c>
       <c r="Z268" t="n">
         <v>812.753</v>
@@ -52442,7 +52468,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG268" t="n">
-        <v>966.8</v>
+        <v>0.9668</v>
       </c>
       <c r="AH268" t="n">
         <v>798.455</v>
@@ -52612,7 +52638,7 @@
         <v>80.5</v>
       </c>
       <c r="Y269" t="n">
-        <v>953</v>
+        <v>0.953</v>
       </c>
       <c r="Z269" t="n">
         <v>812.754</v>
@@ -52636,7 +52662,7 @@
         <v>81.2</v>
       </c>
       <c r="AG269" t="n">
-        <v>961.6</v>
+        <v>0.9616</v>
       </c>
       <c r="AH269" t="n">
         <v>798.456</v>
@@ -52806,7 +52832,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="Y270" t="n">
-        <v>961.1</v>
+        <v>0.9611</v>
       </c>
       <c r="Z270" t="n">
         <v>812.755</v>
@@ -52830,7 +52856,7 @@
         <v>81.5</v>
       </c>
       <c r="AG270" t="n">
-        <v>965.8</v>
+        <v>0.9658</v>
       </c>
       <c r="AH270" t="n">
         <v>798.457</v>
@@ -53000,7 +53026,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="Y271" t="n">
-        <v>955.2</v>
+        <v>0.9552</v>
       </c>
       <c r="Z271" t="n">
         <v>812.7569999999999</v>
@@ -53024,7 +53050,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="AG271" t="n">
-        <v>960.7</v>
+        <v>0.9607</v>
       </c>
       <c r="AH271" t="n">
         <v>798.4589999999999</v>
@@ -53194,7 +53220,7 @@
         <v>81.2</v>
       </c>
       <c r="Y272" t="n">
-        <v>961.9</v>
+        <v>0.9619</v>
       </c>
       <c r="Z272" t="n">
         <v>812.758</v>
@@ -53218,7 +53244,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG272" t="n">
-        <v>966.7</v>
+        <v>0.9667</v>
       </c>
       <c r="AH272" t="n">
         <v>798.46</v>
@@ -53388,7 +53414,7 @@
         <v>81.8</v>
       </c>
       <c r="Y273" t="n">
-        <v>969.2</v>
+        <v>0.9692</v>
       </c>
       <c r="Z273" t="n">
         <v>812.759</v>
@@ -53412,7 +53438,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG273" t="n">
-        <v>966.2</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="AH273" t="n">
         <v>798.461</v>
@@ -53582,7 +53608,7 @@
         <v>82.3</v>
       </c>
       <c r="Y274" t="n">
-        <v>974.9</v>
+        <v>0.9749</v>
       </c>
       <c r="Z274" t="n">
         <v>812.761</v>
@@ -53606,7 +53632,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="AG274" t="n">
-        <v>960.7</v>
+        <v>0.9607</v>
       </c>
       <c r="AH274" t="n">
         <v>798.463</v>
@@ -53776,7 +53802,7 @@
         <v>81.8</v>
       </c>
       <c r="Y275" t="n">
-        <v>968.4</v>
+        <v>0.9684</v>
       </c>
       <c r="Z275" t="n">
         <v>812.7619999999999</v>
@@ -53800,7 +53826,7 @@
         <v>81.3</v>
       </c>
       <c r="AG275" t="n">
-        <v>962.4</v>
+        <v>0.9624</v>
       </c>
       <c r="AH275" t="n">
         <v>798.4640000000001</v>
@@ -53970,7 +53996,7 @@
         <v>82.2</v>
       </c>
       <c r="Y276" t="n">
-        <v>973.2</v>
+        <v>0.9732</v>
       </c>
       <c r="Z276" t="n">
         <v>812.763</v>
@@ -53994,7 +54020,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG276" t="n">
-        <v>965.9</v>
+        <v>0.9659</v>
       </c>
       <c r="AH276" t="n">
         <v>798.465</v>
@@ -54164,7 +54190,7 @@
         <v>82</v>
       </c>
       <c r="Y277" t="n">
-        <v>971.8</v>
+        <v>0.9718</v>
       </c>
       <c r="Z277" t="n">
         <v>812.765</v>
@@ -54188,7 +54214,7 @@
         <v>81.5</v>
       </c>
       <c r="AG277" t="n">
-        <v>964.8</v>
+        <v>0.9648</v>
       </c>
       <c r="AH277" t="n">
         <v>798.467</v>
@@ -54358,7 +54384,7 @@
         <v>81.8</v>
       </c>
       <c r="Y278" t="n">
-        <v>968.6</v>
+        <v>0.9686</v>
       </c>
       <c r="Z278" t="n">
         <v>812.766</v>
@@ -54382,7 +54408,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="AG278" t="n">
-        <v>960.9</v>
+        <v>0.9609</v>
       </c>
       <c r="AH278" t="n">
         <v>798.468</v>
@@ -54552,7 +54578,7 @@
         <v>81.7</v>
       </c>
       <c r="Y279" t="n">
-        <v>967.3</v>
+        <v>0.9673</v>
       </c>
       <c r="Z279" t="n">
         <v>812.7670000000001</v>
@@ -54576,7 +54602,7 @@
         <v>81.5</v>
       </c>
       <c r="AG279" t="n">
-        <v>965.5</v>
+        <v>0.9655</v>
       </c>
       <c r="AH279" t="n">
         <v>798.4690000000001</v>
@@ -54746,7 +54772,7 @@
         <v>81.5</v>
       </c>
       <c r="Y280" t="n">
-        <v>965.2</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="Z280" t="n">
         <v>812.769</v>
@@ -54770,7 +54796,7 @@
         <v>81</v>
       </c>
       <c r="AG280" t="n">
-        <v>959.1</v>
+        <v>0.9591</v>
       </c>
       <c r="AH280" t="n">
         <v>798.471</v>
@@ -54940,7 +54966,7 @@
         <v>81.8</v>
       </c>
       <c r="Y281" t="n">
-        <v>969</v>
+        <v>0.969</v>
       </c>
       <c r="Z281" t="n">
         <v>812.77</v>
@@ -54964,7 +54990,7 @@
         <v>80.8</v>
       </c>
       <c r="AG281" t="n">
-        <v>956.6</v>
+        <v>0.9566</v>
       </c>
       <c r="AH281" t="n">
         <v>798.472</v>
@@ -55134,7 +55160,7 @@
         <v>82.2</v>
       </c>
       <c r="Y282" t="n">
-        <v>973.6</v>
+        <v>0.9736</v>
       </c>
       <c r="Z282" t="n">
         <v>812.772</v>
@@ -55158,7 +55184,7 @@
         <v>80.2</v>
       </c>
       <c r="AG282" t="n">
-        <v>950.2</v>
+        <v>0.9502</v>
       </c>
       <c r="AH282" t="n">
         <v>798.473</v>
@@ -55328,7 +55354,7 @@
         <v>82.3</v>
       </c>
       <c r="Y283" t="n">
-        <v>974.3</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="Z283" t="n">
         <v>812.773</v>
@@ -55352,7 +55378,7 @@
         <v>80.09999999999999</v>
       </c>
       <c r="AG283" t="n">
-        <v>948.6</v>
+        <v>0.9486</v>
       </c>
       <c r="AH283" t="n">
         <v>798.475</v>
@@ -55522,7 +55548,7 @@
         <v>81.8</v>
       </c>
       <c r="Y284" t="n">
-        <v>969.3</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="Z284" t="n">
         <v>812.774</v>
@@ -55546,7 +55572,7 @@
         <v>80.8</v>
       </c>
       <c r="AG284" t="n">
-        <v>956.7</v>
+        <v>0.9567</v>
       </c>
       <c r="AH284" t="n">
         <v>798.476</v>
@@ -55716,7 +55742,7 @@
         <v>82.3</v>
       </c>
       <c r="Y285" t="n">
-        <v>974.6</v>
+        <v>0.9746</v>
       </c>
       <c r="Z285" t="n">
         <v>812.776</v>
@@ -55740,7 +55766,7 @@
         <v>81.2</v>
       </c>
       <c r="AG285" t="n">
-        <v>961.6</v>
+        <v>0.9616</v>
       </c>
       <c r="AH285" t="n">
         <v>798.477</v>
@@ -55910,7 +55936,7 @@
         <v>82.2</v>
       </c>
       <c r="Y286" t="n">
-        <v>974.1</v>
+        <v>0.9741</v>
       </c>
       <c r="Z286" t="n">
         <v>812.777</v>
@@ -55934,7 +55960,7 @@
         <v>80.7</v>
       </c>
       <c r="AG286" t="n">
-        <v>955.6</v>
+        <v>0.9556</v>
       </c>
       <c r="AH286" t="n">
         <v>798.479</v>
@@ -56104,7 +56130,7 @@
         <v>82.8</v>
       </c>
       <c r="Y287" t="n">
-        <v>980.2</v>
+        <v>0.9802</v>
       </c>
       <c r="Z287" t="n">
         <v>812.778</v>
@@ -56128,7 +56154,7 @@
         <v>80.7</v>
       </c>
       <c r="AG287" t="n">
-        <v>956.2</v>
+        <v>0.9562</v>
       </c>
       <c r="AH287" t="n">
         <v>798.48</v>
@@ -56298,7 +56324,7 @@
         <v>82.5</v>
       </c>
       <c r="Y288" t="n">
-        <v>977.1</v>
+        <v>0.9771</v>
       </c>
       <c r="Z288" t="n">
         <v>812.78</v>
@@ -56322,7 +56348,7 @@
         <v>80.5</v>
       </c>
       <c r="AG288" t="n">
-        <v>953.4</v>
+        <v>0.9534</v>
       </c>
       <c r="AH288" t="n">
         <v>798.481</v>
@@ -56492,7 +56518,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="Y289" t="n">
-        <v>983.8</v>
+        <v>0.9838</v>
       </c>
       <c r="Z289" t="n">
         <v>812.7809999999999</v>
@@ -56516,7 +56542,7 @@
         <v>80.3</v>
       </c>
       <c r="AG289" t="n">
-        <v>951.5</v>
+        <v>0.9515</v>
       </c>
       <c r="AH289" t="n">
         <v>798.4829999999999</v>
@@ -56686,7 +56712,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="Y290" t="n">
-        <v>984.1</v>
+        <v>0.9841</v>
       </c>
       <c r="Z290" t="n">
         <v>812.782</v>
@@ -56710,7 +56736,7 @@
         <v>79.90000000000001</v>
       </c>
       <c r="AG290" t="n">
-        <v>945.8</v>
+        <v>0.9458</v>
       </c>
       <c r="AH290" t="n">
         <v>798.484</v>
@@ -56880,7 +56906,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="Y291" t="n">
-        <v>977.8</v>
+        <v>0.9778</v>
       </c>
       <c r="Z291" t="n">
         <v>812.784</v>
@@ -56904,7 +56930,7 @@
         <v>80.5</v>
       </c>
       <c r="AG291" t="n">
-        <v>953.2</v>
+        <v>0.9532</v>
       </c>
       <c r="AH291" t="n">
         <v>798.485</v>
@@ -57074,7 +57100,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="Y292" t="n">
-        <v>969.8</v>
+        <v>0.9698</v>
       </c>
       <c r="Z292" t="n">
         <v>812.785</v>
@@ -57098,7 +57124,7 @@
         <v>80</v>
       </c>
       <c r="AG292" t="n">
-        <v>947.6</v>
+        <v>0.9476</v>
       </c>
       <c r="AH292" t="n">
         <v>798.487</v>
@@ -57268,7 +57294,7 @@
         <v>81.3</v>
       </c>
       <c r="Y293" t="n">
-        <v>963</v>
+        <v>0.963</v>
       </c>
       <c r="Z293" t="n">
         <v>812.7859999999999</v>
@@ -57292,7 +57318,7 @@
         <v>80.40000000000001</v>
       </c>
       <c r="AG293" t="n">
-        <v>952.7</v>
+        <v>0.9527</v>
       </c>
       <c r="AH293" t="n">
         <v>798.4880000000001</v>
@@ -57462,7 +57488,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="Y294" t="n">
-        <v>960.7</v>
+        <v>0.9607</v>
       </c>
       <c r="Z294" t="n">
         <v>812.788</v>
@@ -57486,7 +57512,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="AG294" t="n">
-        <v>958</v>
+        <v>0.958</v>
       </c>
       <c r="AH294" t="n">
         <v>798.489</v>
@@ -57656,7 +57682,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="Y295" t="n">
-        <v>961.1</v>
+        <v>0.9611</v>
       </c>
       <c r="Z295" t="n">
         <v>812.789</v>
@@ -57680,7 +57706,7 @@
         <v>80.5</v>
       </c>
       <c r="AG295" t="n">
-        <v>953.4</v>
+        <v>0.9534</v>
       </c>
       <c r="AH295" t="n">
         <v>798.491</v>
@@ -57850,7 +57876,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="Y296" t="n">
-        <v>954.7</v>
+        <v>0.9547</v>
       </c>
       <c r="Z296" t="n">
         <v>812.79</v>
@@ -57874,7 +57900,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="AG296" t="n">
-        <v>957.9</v>
+        <v>0.9579</v>
       </c>
       <c r="AH296" t="n">
         <v>798.492</v>
@@ -58044,7 +58070,7 @@
         <v>80.3</v>
       </c>
       <c r="Y297" t="n">
-        <v>951.2</v>
+        <v>0.9512</v>
       </c>
       <c r="Z297" t="n">
         <v>812.792</v>
@@ -58068,7 +58094,7 @@
         <v>81.5</v>
       </c>
       <c r="AG297" t="n">
-        <v>964.7</v>
+        <v>0.9647</v>
       </c>
       <c r="AH297" t="n">
         <v>798.4930000000001</v>
@@ -58238,7 +58264,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="Y298" t="n">
-        <v>958.6</v>
+        <v>0.9586</v>
       </c>
       <c r="Z298" t="n">
         <v>812.793</v>
@@ -58262,7 +58288,7 @@
         <v>81.2</v>
       </c>
       <c r="AG298" t="n">
-        <v>961.8</v>
+        <v>0.9618</v>
       </c>
       <c r="AH298" t="n">
         <v>798.495</v>
@@ -58432,7 +58458,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="Y299" t="n">
-        <v>966.6</v>
+        <v>0.9666</v>
       </c>
       <c r="Z299" t="n">
         <v>812.794</v>
@@ -58456,7 +58482,7 @@
         <v>80.8</v>
       </c>
       <c r="AG299" t="n">
-        <v>957.2</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="AH299" t="n">
         <v>798.496</v>
@@ -58626,7 +58652,7 @@
         <v>82.2</v>
       </c>
       <c r="Y300" t="n">
-        <v>973.7</v>
+        <v>0.9737</v>
       </c>
       <c r="Z300" t="n">
         <v>812.796</v>
@@ -58650,7 +58676,7 @@
         <v>81.2</v>
       </c>
       <c r="AG300" t="n">
-        <v>961.2</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="AH300" t="n">
         <v>798.497</v>
@@ -58820,7 +58846,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="Y301" t="n">
-        <v>966</v>
+        <v>0.966</v>
       </c>
       <c r="Z301" t="n">
         <v>812.797</v>
@@ -58844,7 +58870,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AG301" t="n">
-        <v>966.5</v>
+        <v>0.9665</v>
       </c>
       <c r="AH301" t="n">
         <v>798.499</v>
@@ -59014,7 +59040,7 @@
         <v>81.2</v>
       </c>
       <c r="Y302" t="n">
-        <v>961.5</v>
+        <v>0.9615</v>
       </c>
       <c r="Z302" t="n">
         <v>812.798</v>
@@ -59038,7 +59064,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="AG302" t="n">
-        <v>963.8</v>
+        <v>0.9638</v>
       </c>
       <c r="AH302" t="n">
         <v>798.5</v>
@@ -59208,7 +59234,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="Y303" t="n">
-        <v>967</v>
+        <v>0.967</v>
       </c>
       <c r="Z303" t="n">
         <v>812.8</v>
@@ -59232,7 +59258,7 @@
         <v>81.5</v>
       </c>
       <c r="AG303" t="n">
-        <v>965.4</v>
+        <v>0.9654</v>
       </c>
       <c r="AH303" t="n">
         <v>798.501</v>
@@ -59402,7 +59428,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="Y304" t="n">
-        <v>970</v>
+        <v>0.97</v>
       </c>
       <c r="Z304" t="n">
         <v>812.801</v>
@@ -59426,7 +59452,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="AG304" t="n">
-        <v>971.9</v>
+        <v>0.9719</v>
       </c>
       <c r="AH304" t="n">
         <v>798.503</v>
@@ -59596,7 +59622,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="Y305" t="n">
-        <v>967</v>
+        <v>0.967</v>
       </c>
       <c r="Z305" t="n">
         <v>812.802</v>
@@ -59620,7 +59646,7 @@
         <v>81.5</v>
       </c>
       <c r="AG305" t="n">
-        <v>965.4</v>
+        <v>0.9654</v>
       </c>
       <c r="AH305" t="n">
         <v>798.504</v>
@@ -59790,7 +59816,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="Y306" t="n">
-        <v>966.1</v>
+        <v>0.9661</v>
       </c>
       <c r="Z306" t="n">
         <v>812.804</v>
@@ -59814,7 +59840,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG306" t="n">
-        <v>969.7</v>
+        <v>0.9697</v>
       </c>
       <c r="AH306" t="n">
         <v>798.505</v>
@@ -59984,7 +60010,7 @@
         <v>81</v>
       </c>
       <c r="Y307" t="n">
-        <v>959.9</v>
+        <v>0.9599</v>
       </c>
       <c r="Z307" t="n">
         <v>812.8049999999999</v>
@@ -60008,7 +60034,7 @@
         <v>81.8</v>
       </c>
       <c r="AG307" t="n">
-        <v>969.1</v>
+        <v>0.9691</v>
       </c>
       <c r="AH307" t="n">
         <v>798.5069999999999</v>
@@ -60178,7 +60204,7 @@
         <v>80.8</v>
       </c>
       <c r="Y308" t="n">
-        <v>957.5</v>
+        <v>0.9575</v>
       </c>
       <c r="Z308" t="n">
         <v>812.806</v>
@@ -60202,7 +60228,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="AG308" t="n">
-        <v>976.5</v>
+        <v>0.9765</v>
       </c>
       <c r="AH308" t="n">
         <v>798.508</v>
@@ -60372,7 +60398,7 @@
         <v>80.7</v>
       </c>
       <c r="Y309" t="n">
-        <v>955.8</v>
+        <v>0.9558</v>
       </c>
       <c r="Z309" t="n">
         <v>812.808</v>
@@ -60396,7 +60422,7 @@
         <v>82.2</v>
       </c>
       <c r="AG309" t="n">
-        <v>973.2</v>
+        <v>0.9732</v>
       </c>
       <c r="AH309" t="n">
         <v>798.509</v>
@@ -60566,7 +60592,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="Y310" t="n">
-        <v>954.7</v>
+        <v>0.9547</v>
       </c>
       <c r="Z310" t="n">
         <v>812.809</v>
@@ -60590,7 +60616,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="AG310" t="n">
-        <v>978.5</v>
+        <v>0.9785</v>
       </c>
       <c r="AH310" t="n">
         <v>798.511</v>
@@ -60760,7 +60786,7 @@
         <v>80.09999999999999</v>
       </c>
       <c r="Y311" t="n">
-        <v>948.4</v>
+        <v>0.9484</v>
       </c>
       <c r="Z311" t="n">
         <v>812.8099999999999</v>
@@ -60784,7 +60810,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="AG311" t="n">
-        <v>976.2</v>
+        <v>0.9762</v>
       </c>
       <c r="AH311" t="n">
         <v>798.5119999999999</v>
@@ -60954,7 +60980,7 @@
         <v>79.59999999999999</v>
       </c>
       <c r="Y312" t="n">
-        <v>942.6</v>
+        <v>0.9426</v>
       </c>
       <c r="Z312" t="n">
         <v>812.812</v>
@@ -60978,7 +61004,7 @@
         <v>82.8</v>
       </c>
       <c r="AG312" t="n">
-        <v>981</v>
+        <v>0.981</v>
       </c>
       <c r="AH312" t="n">
         <v>798.513</v>
@@ -61148,7 +61174,7 @@
         <v>80.2</v>
       </c>
       <c r="Y313" t="n">
-        <v>950.5</v>
+        <v>0.9505</v>
       </c>
       <c r="Z313" t="n">
         <v>812.813</v>
@@ -61172,7 +61198,7 @@
         <v>82.8</v>
       </c>
       <c r="AG313" t="n">
-        <v>980.6</v>
+        <v>0.9806</v>
       </c>
       <c r="AH313" t="n">
         <v>798.515</v>
@@ -61342,7 +61368,7 @@
         <v>80.2</v>
       </c>
       <c r="Y314" t="n">
-        <v>949.8</v>
+        <v>0.9498</v>
       </c>
       <c r="Z314" t="n">
         <v>812.814</v>
@@ -61366,7 +61392,7 @@
         <v>83.2</v>
       </c>
       <c r="AG314" t="n">
-        <v>985.9</v>
+        <v>0.9859</v>
       </c>
       <c r="AH314" t="n">
         <v>798.516</v>
@@ -61536,7 +61562,7 @@
         <v>80.8</v>
       </c>
       <c r="Y315" t="n">
-        <v>957.2</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="Z315" t="n">
         <v>812.816</v>
@@ -61560,7 +61586,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="AG315" t="n">
-        <v>981.3</v>
+        <v>0.9813</v>
       </c>
       <c r="AH315" t="n">
         <v>798.518</v>
@@ -61730,7 +61756,7 @@
         <v>81.5</v>
       </c>
       <c r="Y316" t="n">
-        <v>965</v>
+        <v>0.965</v>
       </c>
       <c r="Z316" t="n">
         <v>812.817</v>
@@ -61754,7 +61780,7 @@
         <v>82.5</v>
       </c>
       <c r="AG316" t="n">
-        <v>977.6</v>
+        <v>0.9776</v>
       </c>
       <c r="AH316" t="n">
         <v>798.519</v>
@@ -61924,7 +61950,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="Y317" t="n">
-        <v>970</v>
+        <v>0.97</v>
       </c>
       <c r="Z317" t="n">
         <v>812.818</v>
@@ -61948,7 +61974,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG317" t="n">
-        <v>969.8</v>
+        <v>0.9698</v>
       </c>
       <c r="AH317" t="n">
         <v>798.52</v>
@@ -62118,7 +62144,7 @@
         <v>81.3</v>
       </c>
       <c r="Y318" t="n">
-        <v>962.9</v>
+        <v>0.9629</v>
       </c>
       <c r="Z318" t="n">
         <v>812.8200000000001</v>
@@ -62142,7 +62168,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="AG318" t="n">
-        <v>975.8</v>
+        <v>0.9758</v>
       </c>
       <c r="AH318" t="n">
         <v>798.522</v>
@@ -62312,7 +62338,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="Y319" t="n">
-        <v>970.2</v>
+        <v>0.9702</v>
       </c>
       <c r="Z319" t="n">
         <v>812.821</v>
@@ -62336,7 +62362,7 @@
         <v>82.2</v>
       </c>
       <c r="AG319" t="n">
-        <v>973.4</v>
+        <v>0.9734</v>
       </c>
       <c r="AH319" t="n">
         <v>798.523</v>
@@ -62506,7 +62532,7 @@
         <v>81.8</v>
       </c>
       <c r="Y320" t="n">
-        <v>968.5</v>
+        <v>0.9685</v>
       </c>
       <c r="Z320" t="n">
         <v>812.822</v>
@@ -62530,7 +62556,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="AG320" t="n">
-        <v>972.4</v>
+        <v>0.9724</v>
       </c>
       <c r="AH320" t="n">
         <v>798.524</v>
@@ -62700,7 +62726,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="Y321" t="n">
-        <v>975.7</v>
+        <v>0.9757</v>
       </c>
       <c r="Z321" t="n">
         <v>812.824</v>
@@ -62724,7 +62750,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG321" t="n">
-        <v>969.7</v>
+        <v>0.9697</v>
       </c>
       <c r="AH321" t="n">
         <v>798.526</v>
@@ -62894,7 +62920,7 @@
         <v>82.2</v>
       </c>
       <c r="Y322" t="n">
-        <v>973.8</v>
+        <v>0.9738</v>
       </c>
       <c r="Z322" t="n">
         <v>812.825</v>
@@ -62918,7 +62944,7 @@
         <v>81.7</v>
       </c>
       <c r="AG322" t="n">
-        <v>967.9</v>
+        <v>0.9679</v>
       </c>
       <c r="AH322" t="n">
         <v>798.527</v>
@@ -63088,7 +63114,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="Y323" t="n">
-        <v>978.3</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="Z323" t="n">
         <v>812.827</v>
@@ -63112,7 +63138,7 @@
         <v>82</v>
       </c>
       <c r="AG323" t="n">
-        <v>970.9</v>
+        <v>0.9709</v>
       </c>
       <c r="AH323" t="n">
         <v>798.528</v>
@@ -63282,7 +63308,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="Y324" t="n">
-        <v>972.1</v>
+        <v>0.9721</v>
       </c>
       <c r="Z324" t="n">
         <v>812.828</v>
@@ -63306,7 +63332,7 @@
         <v>82.2</v>
       </c>
       <c r="AG324" t="n">
-        <v>973.4</v>
+        <v>0.9734</v>
       </c>
       <c r="AH324" t="n">
         <v>798.53</v>
@@ -63476,7 +63502,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="Y325" t="n">
-        <v>975.6</v>
+        <v>0.9756</v>
       </c>
       <c r="Z325" t="n">
         <v>812.829</v>
@@ -63500,7 +63526,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="AG325" t="n">
-        <v>972.6</v>
+        <v>0.9726</v>
       </c>
       <c r="AH325" t="n">
         <v>798.5309999999999</v>
@@ -63670,7 +63696,7 @@
         <v>82.3</v>
       </c>
       <c r="Y326" t="n">
-        <v>974.2</v>
+        <v>0.9742</v>
       </c>
       <c r="Z326" t="n">
         <v>812.831</v>
@@ -63694,7 +63720,7 @@
         <v>81.8</v>
       </c>
       <c r="AG326" t="n">
-        <v>969</v>
+        <v>0.969</v>
       </c>
       <c r="AH326" t="n">
         <v>798.532</v>
@@ -63864,7 +63890,7 @@
         <v>82.5</v>
       </c>
       <c r="Y327" t="n">
-        <v>977.6</v>
+        <v>0.9776</v>
       </c>
       <c r="Z327" t="n">
         <v>812.832</v>
@@ -63888,7 +63914,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="AG327" t="n">
-        <v>964.2</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="AH327" t="n">
         <v>798.534</v>
@@ -64058,7 +64084,7 @@
         <v>82.5</v>
       </c>
       <c r="Y328" t="n">
-        <v>977.7</v>
+        <v>0.9777</v>
       </c>
       <c r="Z328" t="n">
         <v>812.833</v>
@@ -64082,7 +64108,7 @@
         <v>81.3</v>
       </c>
       <c r="AG328" t="n">
-        <v>962.4</v>
+        <v>0.9624</v>
       </c>
       <c r="AH328" t="n">
         <v>798.535</v>
@@ -64252,7 +64278,7 @@
         <v>82.7</v>
       </c>
       <c r="Y329" t="n">
-        <v>979.4</v>
+        <v>0.9794</v>
       </c>
       <c r="Z329" t="n">
         <v>812.835</v>
@@ -64276,7 +64302,7 @@
         <v>81.7</v>
       </c>
       <c r="AG329" t="n">
-        <v>967.5</v>
+        <v>0.9675</v>
       </c>
       <c r="AH329" t="n">
         <v>798.5359999999999</v>
@@ -64446,7 +64472,7 @@
         <v>83</v>
       </c>
       <c r="Y330" t="n">
-        <v>983.4</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="Z330" t="n">
         <v>812.836</v>
@@ -64470,7 +64496,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="AG330" t="n">
-        <v>960.6</v>
+        <v>0.9606</v>
       </c>
       <c r="AH330" t="n">
         <v>798.538</v>
@@ -64640,7 +64666,7 @@
         <v>82.8</v>
       </c>
       <c r="Y331" t="n">
-        <v>980.8</v>
+        <v>0.9808</v>
       </c>
       <c r="Z331" t="n">
         <v>812.837</v>
@@ -64664,7 +64690,7 @@
         <v>81.3</v>
       </c>
       <c r="AG331" t="n">
-        <v>962.6</v>
+        <v>0.9626</v>
       </c>
       <c r="AH331" t="n">
         <v>798.539</v>
@@ -64834,7 +64860,7 @@
         <v>82.8</v>
       </c>
       <c r="Y332" t="n">
-        <v>980.4</v>
+        <v>0.9804</v>
       </c>
       <c r="Z332" t="n">
         <v>812.8390000000001</v>
@@ -64858,7 +64884,7 @@
         <v>80.8</v>
       </c>
       <c r="AG332" t="n">
-        <v>956.5</v>
+        <v>0.9565</v>
       </c>
       <c r="AH332" t="n">
         <v>798.54</v>
@@ -65028,7 +65054,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="Y333" t="n">
-        <v>981.3</v>
+        <v>0.9813</v>
       </c>
       <c r="Z333" t="n">
         <v>812.84</v>
@@ -65052,7 +65078,7 @@
         <v>80.7</v>
       </c>
       <c r="AG333" t="n">
-        <v>955.5</v>
+        <v>0.9555</v>
       </c>
       <c r="AH333" t="n">
         <v>798.542</v>
@@ -65222,7 +65248,7 @@
         <v>82.3</v>
       </c>
       <c r="Y334" t="n">
-        <v>975.3</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="Z334" t="n">
         <v>812.841</v>
@@ -65246,7 +65272,7 @@
         <v>80.3</v>
       </c>
       <c r="AG334" t="n">
-        <v>951.2</v>
+        <v>0.9512</v>
       </c>
       <c r="AH334" t="n">
         <v>798.543</v>
@@ -65416,7 +65442,7 @@
         <v>82.5</v>
       </c>
       <c r="Y335" t="n">
-        <v>977</v>
+        <v>0.977</v>
       </c>
       <c r="Z335" t="n">
         <v>812.843</v>
@@ -65440,7 +65466,7 @@
         <v>80.40000000000001</v>
       </c>
       <c r="AG335" t="n">
-        <v>952.2</v>
+        <v>0.9522</v>
       </c>
       <c r="AH335" t="n">
         <v>798.544</v>
@@ -65610,7 +65636,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="Y336" t="n">
-        <v>976.3</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="Z336" t="n">
         <v>812.8440000000001</v>
@@ -65634,7 +65660,7 @@
         <v>80</v>
       </c>
       <c r="AG336" t="n">
-        <v>947.9</v>
+        <v>0.9479</v>
       </c>
       <c r="AH336" t="n">
         <v>798.546</v>
@@ -65804,7 +65830,7 @@
         <v>82.2</v>
       </c>
       <c r="Y337" t="n">
-        <v>973.8</v>
+        <v>0.9738</v>
       </c>
       <c r="Z337" t="n">
         <v>812.846</v>
@@ -65828,7 +65854,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="AG337" t="n">
-        <v>954.8</v>
+        <v>0.9548</v>
       </c>
       <c r="AH337" t="n">
         <v>798.547</v>
@@ -65998,7 +66024,7 @@
         <v>82.5</v>
       </c>
       <c r="Y338" t="n">
-        <v>977.5</v>
+        <v>0.9775</v>
       </c>
       <c r="Z338" t="n">
         <v>812.847</v>
@@ -66022,7 +66048,7 @@
         <v>80.40000000000001</v>
       </c>
       <c r="AG338" t="n">
-        <v>951.8</v>
+        <v>0.9518</v>
       </c>
       <c r="AH338" t="n">
         <v>798.548</v>
@@ -66192,7 +66218,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="Y339" t="n">
-        <v>975.6</v>
+        <v>0.9756</v>
       </c>
       <c r="Z339" t="n">
         <v>812.848</v>
@@ -66216,7 +66242,7 @@
         <v>80.09999999999999</v>
       </c>
       <c r="AG339" t="n">
-        <v>948.6</v>
+        <v>0.9486</v>
       </c>
       <c r="AH339" t="n">
         <v>798.55</v>
@@ -66386,7 +66412,7 @@
         <v>82.7</v>
       </c>
       <c r="Y340" t="n">
-        <v>979.7</v>
+        <v>0.9797</v>
       </c>
       <c r="Z340" t="n">
         <v>812.85</v>
@@ -66410,7 +66436,7 @@
         <v>80.2</v>
       </c>
       <c r="AG340" t="n">
-        <v>950.3</v>
+        <v>0.9503</v>
       </c>
       <c r="AH340" t="n">
         <v>798.551</v>
@@ -66580,7 +66606,7 @@
         <v>82.7</v>
       </c>
       <c r="Y341" t="n">
-        <v>979.6</v>
+        <v>0.9796</v>
       </c>
       <c r="Z341" t="n">
         <v>812.851</v>
@@ -66604,7 +66630,7 @@
         <v>79.90000000000001</v>
       </c>
       <c r="AG341" t="n">
-        <v>946.9</v>
+        <v>0.9469</v>
       </c>
       <c r="AH341" t="n">
         <v>798.552</v>
@@ -66774,7 +66800,7 @@
         <v>82.5</v>
       </c>
       <c r="Y342" t="n">
-        <v>977.7</v>
+        <v>0.9777</v>
       </c>
       <c r="Z342" t="n">
         <v>812.852</v>
@@ -66798,7 +66824,7 @@
         <v>80</v>
       </c>
       <c r="AG342" t="n">
-        <v>948.1</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="AH342" t="n">
         <v>798.554</v>
@@ -66968,7 +66994,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="Y343" t="n">
-        <v>975.6</v>
+        <v>0.9756</v>
       </c>
       <c r="Z343" t="n">
         <v>812.854</v>
@@ -66992,7 +67018,7 @@
         <v>80.5</v>
       </c>
       <c r="AG343" t="n">
-        <v>953</v>
+        <v>0.953</v>
       </c>
       <c r="AH343" t="n">
         <v>798.5549999999999</v>
@@ -67162,7 +67188,7 @@
         <v>81.8</v>
       </c>
       <c r="Y344" t="n">
-        <v>968.8</v>
+        <v>0.9688</v>
       </c>
       <c r="Z344" t="n">
         <v>812.855</v>
@@ -67186,7 +67212,7 @@
         <v>80.09999999999999</v>
       </c>
       <c r="AG344" t="n">
-        <v>948.4</v>
+        <v>0.9484</v>
       </c>
       <c r="AH344" t="n">
         <v>798.556</v>
@@ -67356,7 +67382,7 @@
         <v>82</v>
       </c>
       <c r="Y345" t="n">
-        <v>971.6</v>
+        <v>0.9716</v>
       </c>
       <c r="Z345" t="n">
         <v>812.856</v>
@@ -67380,7 +67406,7 @@
         <v>80.2</v>
       </c>
       <c r="AG345" t="n">
-        <v>949.8</v>
+        <v>0.9498</v>
       </c>
       <c r="AH345" t="n">
         <v>798.558</v>
@@ -67550,7 +67576,7 @@
         <v>81.5</v>
       </c>
       <c r="Y346" t="n">
-        <v>965.2</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="Z346" t="n">
         <v>812.8579999999999</v>
@@ -67574,7 +67600,7 @@
         <v>80.2</v>
       </c>
       <c r="AG346" t="n">
-        <v>949.5</v>
+        <v>0.9495</v>
       </c>
       <c r="AH346" t="n">
         <v>798.559</v>
@@ -67744,7 +67770,7 @@
         <v>81.3</v>
       </c>
       <c r="Y347" t="n">
-        <v>962.6</v>
+        <v>0.9626</v>
       </c>
       <c r="Z347" t="n">
         <v>812.859</v>
@@ -67768,7 +67794,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="AG347" t="n">
-        <v>954.1</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="AH347" t="n">
         <v>798.5599999999999</v>
@@ -67938,7 +67964,7 @@
         <v>81.8</v>
       </c>
       <c r="Y348" t="n">
-        <v>969.3</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="Z348" t="n">
         <v>812.86</v>
@@ -67962,7 +67988,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="AG348" t="n">
-        <v>961.1</v>
+        <v>0.9611</v>
       </c>
       <c r="AH348" t="n">
         <v>798.562</v>
@@ -68132,7 +68158,7 @@
         <v>81.8</v>
       </c>
       <c r="Y349" t="n">
-        <v>968.4</v>
+        <v>0.9684</v>
       </c>
       <c r="Z349" t="n">
         <v>812.862</v>
@@ -68156,7 +68182,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="AG349" t="n">
-        <v>960.3</v>
+        <v>0.9603</v>
       </c>
       <c r="AH349" t="n">
         <v>798.563</v>
@@ -68326,7 +68352,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="Y350" t="n">
-        <v>966.7</v>
+        <v>0.9667</v>
       </c>
       <c r="Z350" t="n">
         <v>812.8630000000001</v>
@@ -68350,7 +68376,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="AG350" t="n">
-        <v>964.5</v>
+        <v>0.9645</v>
       </c>
       <c r="AH350" t="n">
         <v>798.564</v>
@@ -68520,7 +68546,7 @@
         <v>81.7</v>
       </c>
       <c r="Y351" t="n">
-        <v>967.9</v>
+        <v>0.9679</v>
       </c>
       <c r="Z351" t="n">
         <v>812.864</v>
@@ -68544,7 +68570,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="AG351" t="n">
-        <v>964.6</v>
+        <v>0.9646</v>
       </c>
       <c r="AH351" t="n">
         <v>798.566</v>
@@ -68714,7 +68740,7 @@
         <v>82</v>
       </c>
       <c r="Y352" t="n">
-        <v>971.7</v>
+        <v>0.9717</v>
       </c>
       <c r="Z352" t="n">
         <v>812.866</v>
@@ -68738,7 +68764,7 @@
         <v>81.2</v>
       </c>
       <c r="AG352" t="n">
-        <v>962</v>
+        <v>0.962</v>
       </c>
       <c r="AH352" t="n">
         <v>798.567</v>
@@ -68908,7 +68934,7 @@
         <v>82.3</v>
       </c>
       <c r="Y353" t="n">
-        <v>974.9</v>
+        <v>0.9749</v>
       </c>
       <c r="Z353" t="n">
         <v>812.867</v>
@@ -68932,7 +68958,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="AG353" t="n">
-        <v>958.4</v>
+        <v>0.9584</v>
       </c>
       <c r="AH353" t="n">
         <v>798.568</v>
@@ -69102,7 +69128,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="Y354" t="n">
-        <v>971.9</v>
+        <v>0.9719</v>
       </c>
       <c r="Z354" t="n">
         <v>812.8680000000001</v>
@@ -69126,7 +69152,7 @@
         <v>80.40000000000001</v>
       </c>
       <c r="AG354" t="n">
-        <v>952.4</v>
+        <v>0.9524</v>
       </c>
       <c r="AH354" t="n">
         <v>798.5700000000001</v>
@@ -69296,7 +69322,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="Y355" t="n">
-        <v>975.9</v>
+        <v>0.9759</v>
       </c>
       <c r="Z355" t="n">
         <v>812.87</v>
@@ -69320,7 +69346,7 @@
         <v>80</v>
       </c>
       <c r="AG355" t="n">
-        <v>947.6</v>
+        <v>0.9476</v>
       </c>
       <c r="AH355" t="n">
         <v>798.571</v>
@@ -69490,7 +69516,7 @@
         <v>82.7</v>
       </c>
       <c r="Y356" t="n">
-        <v>980.1</v>
+        <v>0.9801</v>
       </c>
       <c r="Z356" t="n">
         <v>812.871</v>
@@ -69514,7 +69540,7 @@
         <v>80.09999999999999</v>
       </c>
       <c r="AG356" t="n">
-        <v>948.6</v>
+        <v>0.9486</v>
       </c>
       <c r="AH356" t="n">
         <v>798.572</v>
@@ -69684,7 +69710,7 @@
         <v>82.8</v>
       </c>
       <c r="Y357" t="n">
-        <v>980.6</v>
+        <v>0.9806</v>
       </c>
       <c r="Z357" t="n">
         <v>812.873</v>
@@ -69708,7 +69734,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="AG357" t="n">
-        <v>955.2</v>
+        <v>0.9552</v>
       </c>
       <c r="AH357" t="n">
         <v>798.573</v>
@@ -69878,7 +69904,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="Y358" t="n">
-        <v>978.9</v>
+        <v>0.9789</v>
       </c>
       <c r="Z358" t="n">
         <v>812.874</v>
@@ -69902,7 +69928,7 @@
         <v>80.8</v>
       </c>
       <c r="AG358" t="n">
-        <v>957.1</v>
+        <v>0.9571</v>
       </c>
       <c r="AH358" t="n">
         <v>798.575</v>
@@ -70072,7 +70098,7 @@
         <v>82.2</v>
       </c>
       <c r="Y359" t="n">
-        <v>973.1</v>
+        <v>0.9731</v>
       </c>
       <c r="Z359" t="n">
         <v>812.875</v>
@@ -70096,7 +70122,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="AG359" t="n">
-        <v>960</v>
+        <v>0.96</v>
       </c>
       <c r="AH359" t="n">
         <v>798.576</v>
@@ -70266,7 +70292,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="Y360" t="n">
-        <v>978.2</v>
+        <v>0.9782</v>
       </c>
       <c r="Z360" t="n">
         <v>812.877</v>
@@ -70290,7 +70316,7 @@
         <v>81</v>
       </c>
       <c r="AG360" t="n">
-        <v>959.7</v>
+        <v>0.9597</v>
       </c>
       <c r="AH360" t="n">
         <v>798.577</v>
@@ -70460,7 +70486,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="Y361" t="n">
-        <v>975.4</v>
+        <v>0.9754</v>
       </c>
       <c r="Z361" t="n">
         <v>812.878</v>
@@ -70484,7 +70510,7 @@
         <v>81</v>
       </c>
       <c r="AG361" t="n">
-        <v>959</v>
+        <v>0.959</v>
       </c>
       <c r="AH361" t="n">
         <v>798.579</v>
@@ -70654,7 +70680,7 @@
         <v>82.2</v>
       </c>
       <c r="Y362" t="n">
-        <v>973.7</v>
+        <v>0.9737</v>
       </c>
       <c r="Z362" t="n">
         <v>812.879</v>
@@ -70678,7 +70704,7 @@
         <v>80.7</v>
       </c>
       <c r="AG362" t="n">
-        <v>955.9</v>
+        <v>0.9559</v>
       </c>
       <c r="AH362" t="n">
         <v>798.58</v>
@@ -70848,7 +70874,7 @@
         <v>82.5</v>
       </c>
       <c r="Y363" t="n">
-        <v>977.6</v>
+        <v>0.9776</v>
       </c>
       <c r="Z363" t="n">
         <v>812.881</v>
@@ -70872,7 +70898,7 @@
         <v>80.7</v>
       </c>
       <c r="AG363" t="n">
-        <v>955.4</v>
+        <v>0.9554</v>
       </c>
       <c r="AH363" t="n">
         <v>798.581</v>
@@ -71042,7 +71068,7 @@
         <v>82.2</v>
       </c>
       <c r="Y364" t="n">
-        <v>973.2</v>
+        <v>0.9732</v>
       </c>
       <c r="Z364" t="n">
         <v>812.8819999999999</v>
@@ -71066,7 +71092,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="AG364" t="n">
-        <v>954.1</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="AH364" t="n">
         <v>798.583</v>
@@ -71236,7 +71262,7 @@
         <v>81.5</v>
       </c>
       <c r="Y365" t="n">
-        <v>965.9</v>
+        <v>0.9659</v>
       </c>
       <c r="Z365" t="n">
         <v>812.883</v>
@@ -71260,7 +71286,7 @@
         <v>80.8</v>
       </c>
       <c r="AG365" t="n">
-        <v>957</v>
+        <v>0.957</v>
       </c>
       <c r="AH365" t="n">
         <v>798.5839999999999</v>
@@ -71430,7 +71456,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="Y366" t="n">
-        <v>972.7</v>
+        <v>0.9727</v>
       </c>
       <c r="Z366" t="n">
         <v>812.885</v>
@@ -71454,7 +71480,7 @@
         <v>81.3</v>
       </c>
       <c r="AG366" t="n">
-        <v>962.8</v>
+        <v>0.9628</v>
       </c>
       <c r="AH366" t="n">
         <v>798.585</v>
@@ -71561,4 +71587,2011 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F62"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="110" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>COLUMN (row 2 of TIMESERIES)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>COMPONENT</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>ONTOLOGY PROPERTY (tws:)</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-LATITUDE-IN-DEG</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>twVesselLatitudeInDeg (proposed)</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Position; no navigation module in the ontology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-LONGITUDE-IN-DEG</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>twVesselLongitudeInDeg (proposed)</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Position; no navigation module in the ontology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-HEADING-IN-DEG</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>twVesselHeadingInDeg (proposed)</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Heading, true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-COURSE-OVER-GROUND-IN-DEG</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>twVesselCourseOverGroundInDeg (proposed)</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Course over ground, true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-SPEED-OVER-GROUND-IN-KN</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>twVesselSpeedOverGroundInKn (proposed)</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>kn</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Speed over ground.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-SPEED-THROUGH-WATER-IN-KN</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>twVesselSpeedThroughWaterInKn (proposed)</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>kn</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Speed through the water.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-RATE-OF-TURN-IN-DEG_PER_MIN</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>twVesselRateOfTurnInDegPerMin (proposed)</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>°/min</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Rate of turn, starboard positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-DRAFT-FORE-IN-M</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>twVesselDraftForInM (proposed)</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Current draught at the fore; the ontology has only the maximum (twVesselDraftForMaxInM).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-DRAFT-AFT-IN-M</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>twVesselDraftAftInM (proposed)</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Current draught at the aft; the ontology has only the maximum (twVesselDraftAftMaxInM).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-ROLL-IN-DEG</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>twVesselRollInDeg (proposed)</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Roll, starboard down positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-PITCH-IN-DEG</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>twVesselPitchInDeg (proposed)</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Pitch, bow up positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-HEAVE-IN-M</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>twVesselHeaveInM (proposed)</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Heave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-OPERATIONAL-MODE</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>twVesselOperationalMode (proposed)</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Operational mode; for draft_time_mode.ttl.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-AUTONOMY-LEVEL</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>twVesselAutonomyLevel (proposed)</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Level of autonomy, L0-L4; for draft_time_mode.ttl.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-DISTANCE-TO-GO-IN-NM</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>twVesselDistanceToGoInNm (proposed)</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Distance left on the voyage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-TRUE-WIND-SPEED-IN-KN</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>twWeatherTrueWindSpeedInKn (proposed)</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>kn</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>For weatherconditions.ttl, which has no properties yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-TRUE-WIND-DIRECTION-IN-DEG</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>twWeatherTrueWindFromInDeg (proposed)</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>The bearing the wind blows from, true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-SIGNIFICANT-WAVE-HEIGHT-IN-M</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>twWeatherSignificantWaveHeightInM (proposed)</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Significant wave height.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-CLOUD-COVER-PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>twWeatherCloudCoverPercentage (proposed)</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Cloud cover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1.TWINSHIP-PRECIPITATION-IN-MM_PER_HR</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>FV-RR-1</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>twWeatherPrecipitationInMMPerHr (proposed)</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>mm/h</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Precipitation rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FV-GN-1.TWINSHIP-DIESEL-ENGINE-SPEED-IN-REV-PER-MIN</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FV-GN-1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>twDieselEngineSpeedInRevPerMin</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>rev/min</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Named as extraction.py names the conventional vessels' engines' speed (harmonised to this property). The futuristic genset sheet holds only the maximum speed (twShaftSpeedMaxInRevPerMin).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>FV-GN-1.TWINSHIP-GENERATOR-POWER-IN-KW</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>FV-GN-1</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>twGeneratorPowerInKW (proposed)</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Current output; the ontology has only the maximum (twGeneratorPowerMaxInKW).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>FV-GN-1.TWINSHIP-LOAD-PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>FV-GN-1</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>twGensetLoadPercentage (proposed)</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Load, as a share of the genset's rated power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FV-GN-1.TWINSHIP-FUEL-CONSUMPTION-RATE-IN-MT_PER_HR</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FV-GN-1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>twFuelConsumptionRateInMTPerHr</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MT/h</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fuel consumption rate in metric tons per hour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FV-GN-1.TWINSHIP-FUEL-CONSUMPTION-TOTAL-IN-MT</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FV-GN-1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>twFuelConsumptionTotalInMT</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Total fuel consumption in metric tons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FV-GN-1.TWINSHIP-ME-COOLING-WATER-TEMPERATURE-IN-°C</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FV-GN-1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>twMeCoolingWaterTemperatureInDegC</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>The ontology has this property, but the pipeline extracts only the maximum (TWINSHIP-ME-COOLING-WATER-TEMPERATURE-MAX-IN-°C). This is that name without MAX: to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>FV-GN-1.TWINSHIP-EXHAUST-GAS-TEMPERATURE-MAX-IN-°C</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>FV-GN-1</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>twExhaustGasTemperatureMaxInDegC (proposed)</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Hottest cylinder's exhaust gas temperature; the ontology's exhaust properties are the boiler's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>FV-GN-1.TWINSHIP-EXHAUST-GAS-TEMPERATURE-MAX-CYLINDER</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>FV-GN-1</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>twExhaustGasTemperatureMaxCylinder (proposed)</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Which cylinder is the hottest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FV-GN-2.TWINSHIP-DIESEL-ENGINE-SPEED-IN-REV-PER-MIN</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FV-GN-2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>twDieselEngineSpeedInRevPerMin</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>rev/min</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Named as extraction.py names the conventional vessels' engines' speed (harmonised to this property). The futuristic genset sheet holds only the maximum speed (twShaftSpeedMaxInRevPerMin).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>FV-GN-2.TWINSHIP-GENERATOR-POWER-IN-KW</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>FV-GN-2</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>twGeneratorPowerInKW (proposed)</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Current output; the ontology has only the maximum (twGeneratorPowerMaxInKW).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>FV-GN-2.TWINSHIP-LOAD-PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>FV-GN-2</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>twGensetLoadPercentage (proposed)</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Load, as a share of the genset's rated power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FV-GN-2.TWINSHIP-FUEL-CONSUMPTION-RATE-IN-MT_PER_HR</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FV-GN-2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>twFuelConsumptionRateInMTPerHr</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>MT/h</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Fuel consumption rate in metric tons per hour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>FV-GN-2.TWINSHIP-FUEL-CONSUMPTION-TOTAL-IN-MT</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FV-GN-2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>twFuelConsumptionTotalInMT</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Total fuel consumption in metric tons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>FV-GN-2.TWINSHIP-ME-COOLING-WATER-TEMPERATURE-IN-°C</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FV-GN-2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>twMeCoolingWaterTemperatureInDegC</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>The ontology has this property, but the pipeline extracts only the maximum (TWINSHIP-ME-COOLING-WATER-TEMPERATURE-MAX-IN-°C). This is that name without MAX: to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>FV-GN-2.TWINSHIP-EXHAUST-GAS-TEMPERATURE-MAX-IN-°C</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>FV-GN-2</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>twExhaustGasTemperatureMaxInDegC (proposed)</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Hottest cylinder's exhaust gas temperature; the ontology's exhaust properties are the boiler's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>FV-GN-2.TWINSHIP-EXHAUST-GAS-TEMPERATURE-MAX-CYLINDER</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>FV-GN-2</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>twExhaustGasTemperatureMaxCylinder (proposed)</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Which cylinder is the hottest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>FV-ESS-1.TWINSHIP-ESS-STATE-OF-CHARGE-PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>FV-ESS-1</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>twESSStateOfChargePercentage (proposed)</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>The ontology has only the depth of discharge (twESSDepthOfDischargePercentage).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>FV-ESS-1.TWINSHIP-ESS-POWER-IN-KW</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>FV-ESS-1</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>twESSPowerInKW (proposed)</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Charge (+) or discharge power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>FV-EMSH-1.TWINSHIP-EMSH-POWER-IN-KW</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>FV-EMSH-1</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>twEMSHPowerInKW (proposed)</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Shaft power; twEMPowerInMWh is the motor's capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>FV-EMSH-1.TWINSHIP-EMSH-SPEED-REV-PER-MIN</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FV-EMSH-1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>twEMSHSpeedInRevPerMin</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>rev/min</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Electric motor shaft rotational speed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>FV-EMSH-1.TWINSHIP-EMSH-TORQUE-kN</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FV-EMSH-1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>twEMSHTorqueInKN</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>kN [sic]</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Electric motor shaft torque. The ontology says kilonewtons; a torque is kN·m and the values here are kN·m: to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>FV-EMSH-2.TWINSHIP-EMSH-POWER-IN-KW</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>FV-EMSH-2</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>twEMSHPowerInKW (proposed)</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Shaft power; twEMPowerInMWh is the motor's capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>FV-EMSH-2.TWINSHIP-EMSH-SPEED-REV-PER-MIN</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FV-EMSH-2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>twEMSHSpeedInRevPerMin</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>rev/min</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Electric motor shaft rotational speed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FV-EMSH-2.TWINSHIP-EMSH-TORQUE-kN</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>FV-EMSH-2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>twEMSHTorqueInKN</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>kN [sic]</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Electric motor shaft torque. The ontology says kilonewtons; a torque is kN·m and the values here are kN·m: to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>FV-CPP-1.TWINSHIP-CPP-PITCH-PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>FV-CPP-1</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>twPropellerPitchInPercentage (proposed)</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Current pitch; the ontology has only the maximum (twPropellerPitchMaxInPercentage).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>FV-CPP-1.TWINSHIP-RUDDER-ANGLE-DEGREE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>FV-CPP-1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>twRudderAngleDegree</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Rudder angle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>FV-CPP-2.TWINSHIP-CPP-PITCH-PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>FV-CPP-2</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>twPropellerPitchInPercentage (proposed)</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>Current pitch; the ontology has only the maximum (twPropellerPitchMaxInPercentage).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>FV-CPP-2.TWINSHIP-RUDDER-ANGLE-DEGREE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FV-CPP-2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>twRudderAngleDegree</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Rudder angle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>FV-WASP-1.TWINSHIP-WASP-POWER-kW</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FV-WASP-1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>twWASPPowerInKW</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Wind Assisted Propulsion System power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>FV-WASP-1.TWINSHIP-WASP-POWER-REDUCTION-EFFICIENCY-PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FV-WASP-1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>twWASPPowerReductionEfficiencyPercentage</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Wind Assisted Propulsion System power reduction efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>FV-WASP-1.TWINSHIP-WASP-THRUST-IN-kN</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>FV-WASP-1</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>twWASPThrustInKN (proposed)</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>kN</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Thrust from the sail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>FV-WASP-1.TWINSHIP-WASP-FAN-SPEED-IN-REV_PER_MIN</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>FV-WASP-1</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>twWASPFanSpeedInRevPerMin (proposed)</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>rev/min</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Speed of the suction fan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>FV-WASP-2.TWINSHIP-WASP-POWER-kW</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>FV-WASP-2</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>twWASPPowerInKW</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Wind Assisted Propulsion System power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>FV-WASP-2.TWINSHIP-WASP-POWER-REDUCTION-EFFICIENCY-PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>FV-WASP-2</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>twWASPPowerReductionEfficiencyPercentage</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Wind Assisted Propulsion System power reduction efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>FV-WASP-2.TWINSHIP-WASP-THRUST-IN-kN</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>FV-WASP-2</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>twWASPThrustInKN (proposed)</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>kN</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Thrust from the sail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>FV-WASP-2.TWINSHIP-WASP-FAN-SPEED-IN-REV_PER_MIN</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>FV-WASP-2</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>twWASPFanSpeedInRevPerMin (proposed)</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>rev/min</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>Speed of the suction fan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>SG-01.TWINSHIP-BENDING-STRESS-PERCENTAGE-OF-ALLOWABLE</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>SG-01</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>twStrainGaugeBendingStressPercentageOfAllowable (proposed)</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>Hull structural monitoring; new.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>SG-02.TWINSHIP-BENDING-STRESS-PERCENTAGE-OF-ALLOWABLE</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>SG-02</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>twStrainGaugeBendingStressPercentageOfAllowable (proposed)</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>Hull structural monitoring; new.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>SG-03.TWINSHIP-BENDING-STRESS-PERCENTAGE-OF-ALLOWABLE</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>SG-03</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>twStrainGaugeBendingStressPercentageOfAllowable (proposed)</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Hull structural monitoring; new.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>SG-04.TWINSHIP-BENDING-STRESS-PERCENTAGE-OF-ALLOWABLE</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>SG-04</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>twStrainGaugeBendingStressPercentageOfAllowable (proposed)</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>Hull structural monitoring; new.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>SG-05.TWINSHIP-BENDING-STRESS-PERCENTAGE-OF-ALLOWABLE</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>SG-05</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>twStrainGaugeBendingStressPercentageOfAllowable (proposed)</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Hull structural monitoring; new.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F62"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>